--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -74015,13 +74015,13 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O406" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="R406" t="n">
-        <v>1.085073594227124</v>
+        <v>1.102861685935765</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
@@ -74179,10 +74179,10 @@
         </is>
       </c>
       <c r="N407" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O407" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="U407" t="inlineStr">
         <is>
@@ -74927,12 +74927,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -74966,81 +74966,100 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="O411" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="R411" t="n">
-        <v>0.02120128218249345</v>
+        <v>0.2055873694222336</v>
       </c>
       <c r="S411" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U411" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="AA411" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO411" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP411" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ411" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR411" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS411" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS411" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT411" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU411" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV411" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW411" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX411" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY411" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ411" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA411" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB411" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC411" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -75067,17 +75086,17 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -75102,7 +75121,7 @@
       </c>
       <c r="L412" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
@@ -75111,81 +75130,175 @@
         </is>
       </c>
       <c r="N412" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="O412" t="n">
-        <v>70</v>
-      </c>
-      <c r="R412" t="n">
-        <v>0.05717658852960364</v>
-      </c>
-      <c r="S412" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="U412" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W412" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X412" t="inlineStr">
+        <is>
+          <t>Kikhosta</t>
+        </is>
+      </c>
+      <c r="Y412" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z412" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA412" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB412" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC412" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD412" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE412" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF412" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG412" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH412" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI412" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ412" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK412" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM412" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN412" t="b">
+        <v>1</v>
       </c>
       <c r="AO412" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP412" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ412" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR412" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS412" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS412" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT412" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU412" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV412" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW412" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX412" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY412" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ412" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA412" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB412" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC412" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -75217,12 +75330,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -75247,7 +75360,7 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
@@ -75256,93 +75369,81 @@
         </is>
       </c>
       <c r="N413" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="O413" t="n">
-        <v>2</v>
-      </c>
-      <c r="P413" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="R413" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.02120128218249345</v>
       </c>
       <c r="S413" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA413" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO413" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP413" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ413" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS413" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR413" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS413" t="inlineStr"/>
       <c r="AT413" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU413" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV413" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW413" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX413" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY413" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ413" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA413" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB413" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC413" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -75369,17 +75470,17 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -75413,173 +75514,81 @@
         </is>
       </c>
       <c r="N414" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="O414" t="n">
-        <v>2</v>
-      </c>
-      <c r="P414" t="n">
-        <v>2</v>
-      </c>
-      <c r="U414" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V414" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W414" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X414" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y414" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z414" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA414" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB414" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC414" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD414" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE414" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF414" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG414" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH414" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI414" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ414" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK414" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM414" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN414" t="b">
-        <v>1</v>
+        <v>70</v>
+      </c>
+      <c r="R414" t="n">
+        <v>0.05717658852960364</v>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO414" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP414" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ414" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS414" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR414" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS414" t="inlineStr"/>
       <c r="AT414" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU414" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV414" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW414" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX414" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY414" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ414" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA414" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB414" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC414" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -75611,12 +75620,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -75641,7 +75650,7 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
@@ -75650,81 +75659,93 @@
         </is>
       </c>
       <c r="N415" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="O415" t="n">
-        <v>67</v>
+        <v>2</v>
+      </c>
+      <c r="P415" t="n">
+        <v>2</v>
       </c>
       <c r="R415" t="n">
-        <v>0.01919575548955488</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S415" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA415" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO415" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP415" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR415" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS415" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ415" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS415" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT415" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU415" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV415" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW415" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX415" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY415" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ415" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA415" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB415" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC415" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -75751,17 +75772,17 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -75786,7 +75807,7 @@
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
@@ -75795,81 +75816,173 @@
         </is>
       </c>
       <c r="N416" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="O416" t="n">
-        <v>76</v>
-      </c>
-      <c r="R416" t="n">
-        <v>0.06207743897499823</v>
-      </c>
-      <c r="S416" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P416" t="n">
+        <v>2</v>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W416" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X416" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y416" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z416" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA416" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB416" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC416" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD416" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE416" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF416" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG416" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH416" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI416" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ416" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK416" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM416" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN416" t="b">
+        <v>1</v>
       </c>
       <c r="AO416" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP416" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR416" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS416" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ416" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS416" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT416" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU416" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV416" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW416" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX416" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY416" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ416" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA416" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB416" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC416" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -75901,12 +76014,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -75931,7 +76044,7 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
@@ -75940,93 +76053,81 @@
         </is>
       </c>
       <c r="N417" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="O417" t="n">
-        <v>2</v>
-      </c>
-      <c r="P417" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="R417" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S417" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA417" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO417" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP417" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ417" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS417" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR417" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS417" t="inlineStr"/>
       <c r="AT417" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU417" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV417" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW417" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX417" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY417" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ417" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA417" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB417" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC417" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -76053,17 +76154,17 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -76097,173 +76198,81 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="O418" t="n">
-        <v>2</v>
-      </c>
-      <c r="P418" t="n">
-        <v>2</v>
-      </c>
-      <c r="U418" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V418" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W418" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X418" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y418" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z418" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA418" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB418" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC418" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD418" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE418" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF418" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG418" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH418" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI418" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ418" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK418" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM418" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN418" t="b">
-        <v>1</v>
+        <v>76</v>
+      </c>
+      <c r="R418" t="n">
+        <v>0.06207743897499823</v>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO418" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP418" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ418" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS418" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR418" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS418" t="inlineStr"/>
       <c r="AT418" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU418" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV418" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW418" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX418" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY418" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ418" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA418" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB418" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC418" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -76295,12 +76304,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -76325,7 +76334,7 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
@@ -76334,81 +76343,93 @@
         </is>
       </c>
       <c r="N419" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="O419" t="n">
-        <v>65</v>
+        <v>2</v>
+      </c>
+      <c r="P419" t="n">
+        <v>2</v>
       </c>
       <c r="R419" t="n">
-        <v>0.018622747863001</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S419" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA419" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO419" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP419" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR419" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS419" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ419" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS419" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT419" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU419" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV419" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW419" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX419" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY419" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ419" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA419" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB419" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC419" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -76435,17 +76456,17 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -76470,7 +76491,7 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
@@ -76479,81 +76500,173 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="O420" t="n">
-        <v>28</v>
-      </c>
-      <c r="R420" t="n">
-        <v>0.02287063541184146</v>
-      </c>
-      <c r="S420" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P420" t="n">
+        <v>2</v>
+      </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V420" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W420" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X420" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y420" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z420" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA420" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB420" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC420" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD420" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE420" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF420" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG420" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH420" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI420" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ420" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK420" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM420" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN420" t="b">
+        <v>1</v>
       </c>
       <c r="AO420" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP420" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR420" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS420" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ420" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS420" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT420" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU420" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV420" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW420" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX420" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY420" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ420" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA420" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB420" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC420" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -76585,12 +76698,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -76615,7 +76728,7 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
@@ -76624,93 +76737,81 @@
         </is>
       </c>
       <c r="N421" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="O421" t="n">
-        <v>3</v>
-      </c>
-      <c r="P421" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="R421" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.018622747863001</v>
       </c>
       <c r="S421" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA421" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO421" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP421" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ421" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS421" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR421" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS421" t="inlineStr"/>
       <c r="AT421" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU421" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV421" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW421" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX421" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY421" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ421" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA421" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB421" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC421" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -76737,17 +76838,17 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -76781,173 +76882,81 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="O422" t="n">
-        <v>3</v>
-      </c>
-      <c r="P422" t="n">
-        <v>3</v>
-      </c>
-      <c r="U422" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V422" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W422" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X422" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y422" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z422" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA422" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB422" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC422" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD422" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE422" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF422" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG422" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH422" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI422" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ422" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK422" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM422" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN422" t="b">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="R422" t="n">
+        <v>0.02287063541184146</v>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO422" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP422" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ422" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS422" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR422" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS422" t="inlineStr"/>
       <c r="AT422" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU422" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV422" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW422" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX422" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY422" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ422" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA422" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB422" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC422" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -76979,12 +76988,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -77009,7 +77018,7 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
@@ -77018,81 +77027,93 @@
         </is>
       </c>
       <c r="N423" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="O423" t="n">
-        <v>80</v>
+        <v>3</v>
+      </c>
+      <c r="P423" t="n">
+        <v>3</v>
       </c>
       <c r="R423" t="n">
-        <v>0.02292030506215508</v>
+        <v>0.05079797265291142</v>
       </c>
       <c r="S423" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA423" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO423" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP423" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR423" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS423" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ423" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS423" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT423" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU423" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV423" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW423" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX423" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY423" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ423" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA423" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB423" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC423" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -77119,17 +77140,17 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -77154,7 +77175,7 @@
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
@@ -77163,81 +77184,173 @@
         </is>
       </c>
       <c r="N424" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="O424" t="n">
-        <v>66</v>
-      </c>
-      <c r="R424" t="n">
-        <v>0.05390935489934058</v>
-      </c>
-      <c r="S424" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P424" t="n">
+        <v>3</v>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V424" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W424" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X424" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y424" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z424" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA424" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB424" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC424" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD424" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE424" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF424" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG424" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH424" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI424" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ424" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK424" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM424" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN424" t="b">
+        <v>1</v>
       </c>
       <c r="AO424" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP424" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR424" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS424" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ424" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS424" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT424" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU424" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV424" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW424" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX424" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY424" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ424" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA424" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB424" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC424" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -77269,12 +77382,12 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -77299,7 +77412,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
@@ -77308,93 +77421,81 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="O425" t="n">
-        <v>2</v>
-      </c>
-      <c r="P425" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="R425" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.02292030506215508</v>
       </c>
       <c r="S425" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA425" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO425" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP425" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ425" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS425" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR425" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS425" t="inlineStr"/>
       <c r="AT425" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU425" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV425" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW425" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX425" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY425" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ425" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA425" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB425" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC425" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -77421,17 +77522,17 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -77465,173 +77566,81 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="O426" t="n">
-        <v>2</v>
-      </c>
-      <c r="P426" t="n">
-        <v>2</v>
-      </c>
-      <c r="U426" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V426" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W426" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X426" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y426" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z426" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA426" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB426" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC426" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD426" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE426" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF426" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG426" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH426" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI426" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ426" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK426" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM426" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN426" t="b">
-        <v>1</v>
+        <v>66</v>
+      </c>
+      <c r="R426" t="n">
+        <v>0.05390935489934058</v>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO426" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP426" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ426" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS426" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR426" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS426" t="inlineStr"/>
       <c r="AT426" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU426" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV426" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW426" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX426" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY426" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ426" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA426" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB426" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC426" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -77663,12 +77672,12 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -77693,7 +77702,7 @@
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
@@ -77702,81 +77711,93 @@
         </is>
       </c>
       <c r="N427" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="O427" t="n">
-        <v>67</v>
+        <v>2</v>
+      </c>
+      <c r="P427" t="n">
+        <v>2</v>
       </c>
       <c r="R427" t="n">
-        <v>0.01919575548955488</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S427" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA427" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO427" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP427" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR427" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS427" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ427" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS427" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT427" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU427" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV427" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW427" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX427" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY427" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ427" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA427" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB427" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC427" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -77803,17 +77824,17 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -77838,90 +77859,182 @@
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N428" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="O428" t="n">
-        <v>78</v>
-      </c>
-      <c r="R428" t="n">
-        <v>0.2864793219225436</v>
-      </c>
-      <c r="S428" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P428" t="n">
+        <v>2</v>
+      </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V428" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W428" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X428" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y428" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z428" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA428" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB428" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC428" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD428" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE428" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF428" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG428" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH428" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI428" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ428" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK428" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM428" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN428" t="b">
+        <v>1</v>
       </c>
       <c r="AO428" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP428" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR428" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS428" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ428" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS428" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT428" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU428" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV428" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW428" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX428" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY428" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ428" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA428" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB428" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC428" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -77953,12 +78066,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -77983,109 +78096,90 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N429" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="O429" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="R429" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S429" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U429" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="AA429" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO429" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP429" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ429" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR429" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS429" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS429" t="inlineStr"/>
       <c r="AT429" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU429" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV429" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW429" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX429" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY429" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ429" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA429" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB429" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC429" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -78112,17 +78206,17 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -78156,175 +78250,81 @@
         </is>
       </c>
       <c r="N430" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="O430" t="n">
-        <v>3</v>
-      </c>
-      <c r="U430" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="V430" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="W430" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X430" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y430" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z430" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA430" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB430" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC430" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD430" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="R430" t="n">
+        <v>0.2864793219225436</v>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO430" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP430" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR430" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS430" t="inlineStr"/>
+      <c r="AT430" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU430" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV430" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE430" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF430" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG430" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH430" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI430" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ430" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK430" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
-        </is>
-      </c>
-      <c r="AM430" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN430" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO430" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP430" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ430" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR430" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS430" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="AT430" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU430" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV430" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW430" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX430" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY430" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ430" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA430" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB430" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC430" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -78356,12 +78356,12 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -78395,81 +78395,100 @@
         </is>
       </c>
       <c r="N431" t="n">
+        <v>7</v>
+      </c>
+      <c r="O431" t="n">
+        <v>7</v>
+      </c>
+      <c r="R431" t="n">
+        <v>0.1245166419604896</v>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="AA431" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO431" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP431" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ431" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR431" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS431" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="AT431" t="n">
         <v>2</v>
       </c>
-      <c r="O431" t="n">
-        <v>2</v>
-      </c>
-      <c r="R431" t="n">
-        <v>0.003875939847584092</v>
-      </c>
-      <c r="S431" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO431" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP431" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR431" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS431" t="inlineStr"/>
-      <c r="AT431" t="n">
-        <v>0</v>
-      </c>
       <c r="AU431" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV431" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW431" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX431" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY431" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ431" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA431" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB431" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC431" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -78496,17 +78515,17 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -78540,22 +78559,39 @@
         </is>
       </c>
       <c r="N432" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O432" t="n">
-        <v>6</v>
-      </c>
-      <c r="R432" t="n">
-        <v>0.1061385495477304</v>
-      </c>
-      <c r="S432" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
       </c>
       <c r="U432" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="W432" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X432" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y432" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z432" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA432" t="inlineStr">
@@ -78563,6 +78599,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB432" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC432" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD432" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE432" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF432" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG432" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH432" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI432" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ432" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK432" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
+        </is>
+      </c>
+      <c r="AM432" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN432" t="b">
+        <v>1</v>
+      </c>
       <c r="AO432" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -78575,7 +78669,7 @@
       </c>
       <c r="AQ432" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR432" t="inlineStr">
@@ -78585,7 +78679,7 @@
       </c>
       <c r="AS432" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
+          <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
       <c r="AT432" t="n">
@@ -78593,47 +78687,47 @@
       </c>
       <c r="AU432" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV432" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW432" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX432" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY432" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ432" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA432" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB432" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC432" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -78660,217 +78754,526 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N433" t="n">
+        <v>2</v>
+      </c>
+      <c r="O433" t="n">
+        <v>2</v>
+      </c>
+      <c r="R433" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO433" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP433" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR433" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS433" t="inlineStr"/>
+      <c r="AT433" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU433" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV433" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW433" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX433" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY433" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ433" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA433" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB433" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC433" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N434" t="n">
+        <v>6</v>
+      </c>
+      <c r="O434" t="n">
+        <v>6</v>
+      </c>
+      <c r="R434" t="n">
+        <v>0.1061385495477304</v>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA434" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO434" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP434" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ434" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR434" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS434" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT434" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU434" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV434" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW434" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX434" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY434" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ434" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA434" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB434" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC434" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F433" t="inlineStr">
+      <c r="F435" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G433" t="inlineStr">
+      <c r="G435" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H433" t="inlineStr">
-        <is>
-          <t>D028</t>
-        </is>
-      </c>
-      <c r="I433" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="J433" t="inlineStr">
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
         <is>
           <t>百日咳</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr">
+      <c r="K435" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L433" t="inlineStr">
+      <c r="L435" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M433" t="inlineStr">
+      <c r="M435" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N433" t="n">
+      <c r="N435" t="n">
         <v>6</v>
       </c>
-      <c r="O433" t="n">
+      <c r="O435" t="n">
         <v>6</v>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="U435" t="inlineStr">
         <is>
           <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
-      <c r="V433" t="inlineStr">
+      <c r="V435" t="inlineStr">
         <is>
           <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
-      <c r="W433" t="inlineStr">
+      <c r="W435" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X433" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>Kikhoste</t>
         </is>
       </c>
-      <c r="Y433" t="inlineStr">
+      <c r="Y435" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z433" t="inlineStr">
+      <c r="Z435" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA433" t="inlineStr">
+      <c r="AA435" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB433" t="inlineStr">
+      <c r="AB435" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC433" t="inlineStr">
+      <c r="AC435" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD433" t="inlineStr">
+      <c r="AD435" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE433" t="inlineStr">
+      <c r="AE435" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF433" t="inlineStr">
+      <c r="AF435" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG433" t="inlineStr">
+      <c r="AG435" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH433" t="inlineStr">
+      <c r="AH435" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI433" t="inlineStr">
+      <c r="AI435" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ433" t="inlineStr">
+      <c r="AJ435" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK433" t="inlineStr">
+      <c r="AK435" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM433" t="inlineStr">
+      <c r="AM435" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN433" t="b">
+      <c r="AN435" t="b">
         <v>1</v>
       </c>
-      <c r="AO433" t="inlineStr">
+      <c r="AO435" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP433" t="inlineStr">
+      <c r="AP435" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ433" t="inlineStr">
+      <c r="AQ435" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR433" t="inlineStr">
+      <c r="AR435" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS433" t="inlineStr">
+      <c r="AS435" t="inlineStr">
         <is>
           <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
-      <c r="AT433" t="n">
+      <c r="AT435" t="n">
         <v>2</v>
       </c>
-      <c r="AU433" t="inlineStr">
+      <c r="AU435" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV433" t="inlineStr">
+      <c r="AV435" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW433" t="inlineStr">
+      <c r="AW435" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX433" t="inlineStr">
+      <c r="AX435" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY433" t="inlineStr">
+      <c r="AY435" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ433" t="inlineStr">
+      <c r="AZ435" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA433" t="inlineStr">
+      <c r="BA435" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB433" t="inlineStr">
+      <c r="BB435" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC433" t="inlineStr">
+      <c r="BC435" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -78992,7 +79395,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -79002,7 +79405,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="11">
@@ -79022,7 +79425,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13">
@@ -79054,7 +79457,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29268</v>
+        <v>29295</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -72731,13 +72731,13 @@
         </is>
       </c>
       <c r="N397" t="n">
-        <v>1051</v>
+        <v>1073</v>
       </c>
       <c r="O397" t="n">
-        <v>1051</v>
+        <v>1073</v>
       </c>
       <c r="R397" t="n">
-        <v>3.860125222315299</v>
+        <v>3.940927082344735</v>
       </c>
       <c r="S397" t="inlineStr">
         <is>
@@ -74015,13 +74015,13 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O406" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R406" t="n">
-        <v>1.102861685935765</v>
+        <v>1.120649777644407</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
@@ -74179,10 +74179,10 @@
         </is>
       </c>
       <c r="N407" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O407" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U407" t="inlineStr">
         <is>
@@ -78211,12 +78211,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -78241,22 +78241,22 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N430" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="O430" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="R430" t="n">
-        <v>0.2864793219225436</v>
+        <v>0.04329084560098561</v>
       </c>
       <c r="S430" t="inlineStr">
         <is>
@@ -78289,42 +78289,42 @@
       </c>
       <c r="AV430" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW430" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX430" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY430" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ430" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA430" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB430" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC430" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -78356,12 +78356,12 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -78395,100 +78395,81 @@
         </is>
       </c>
       <c r="N431" t="n">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="O431" t="n">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="R431" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.2864793219225436</v>
       </c>
       <c r="S431" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="AA431" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO431" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP431" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ431" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR431" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS431" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS431" t="inlineStr"/>
       <c r="AT431" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU431" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV431" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW431" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX431" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY431" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ431" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA431" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB431" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC431" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -78515,7 +78496,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -78559,103 +78540,28 @@
         </is>
       </c>
       <c r="N432" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O432" t="n">
-        <v>7</v>
+        <v>11</v>
+      </c>
+      <c r="R432" t="n">
+        <v>0.1956690087950551</v>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U432" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
-      <c r="V432" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="W432" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X432" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y432" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z432" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA432" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB432" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC432" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD432" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE432" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF432" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG432" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH432" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI432" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ432" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK432" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
-        </is>
-      </c>
-      <c r="AM432" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN432" t="b">
-        <v>1</v>
       </c>
       <c r="AO432" t="inlineStr">
         <is>
@@ -78754,17 +78660,17 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -78798,81 +78704,175 @@
         </is>
       </c>
       <c r="N433" t="n">
+        <v>11</v>
+      </c>
+      <c r="O433" t="n">
+        <v>11</v>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="W433" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X433" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y433" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z433" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA433" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB433" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC433" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD433" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE433" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF433" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG433" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH433" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI433" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ433" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK433" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
+        </is>
+      </c>
+      <c r="AM433" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN433" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO433" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP433" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ433" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR433" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS433" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="AT433" t="n">
         <v>2</v>
       </c>
-      <c r="O433" t="n">
-        <v>2</v>
-      </c>
-      <c r="R433" t="n">
-        <v>0.003875939847584092</v>
-      </c>
-      <c r="S433" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO433" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP433" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR433" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS433" t="inlineStr"/>
-      <c r="AT433" t="n">
-        <v>0</v>
-      </c>
       <c r="AU433" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV433" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW433" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ433" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA433" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB433" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC433" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -78904,12 +78904,12 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -78943,100 +78943,81 @@
         </is>
       </c>
       <c r="N434" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O434" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R434" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S434" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA434" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO434" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP434" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ434" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR434" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS434" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS434" t="inlineStr"/>
       <c r="AT434" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU434" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV434" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW434" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX434" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY434" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ434" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA434" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB434" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC434" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -79063,7 +79044,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -79112,98 +79093,23 @@
       <c r="O435" t="n">
         <v>6</v>
       </c>
+      <c r="R435" t="n">
+        <v>0.1061385495477304</v>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U435" t="inlineStr">
         <is>
           <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
-      <c r="V435" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W435" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X435" t="inlineStr">
-        <is>
-          <t>Kikhoste</t>
-        </is>
-      </c>
-      <c r="Y435" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z435" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA435" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB435" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC435" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD435" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE435" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF435" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG435" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH435" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI435" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ435" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK435" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM435" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN435" t="b">
-        <v>1</v>
       </c>
       <c r="AO435" t="inlineStr">
         <is>
@@ -79274,6 +79180,245 @@
         </is>
       </c>
       <c r="BC435" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N436" t="n">
+        <v>6</v>
+      </c>
+      <c r="O436" t="n">
+        <v>6</v>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W436" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X436" t="inlineStr">
+        <is>
+          <t>Kikhoste</t>
+        </is>
+      </c>
+      <c r="Y436" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z436" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB436" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC436" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD436" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE436" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF436" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG436" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH436" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI436" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ436" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK436" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM436" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN436" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO436" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP436" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ436" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR436" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS436" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT436" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU436" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV436" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW436" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX436" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY436" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA436" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB436" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC436" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -79395,7 +79540,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -79405,7 +79550,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11">
@@ -79457,7 +79602,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29295</v>
+        <v>29375</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -72731,13 +72731,13 @@
         </is>
       </c>
       <c r="N397" t="n">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="O397" t="n">
-        <v>1073</v>
+        <v>1078</v>
       </c>
       <c r="R397" t="n">
-        <v>3.940927082344735</v>
+        <v>3.959291141442334</v>
       </c>
       <c r="S397" t="inlineStr">
         <is>
@@ -74563,13 +74563,13 @@
         </is>
       </c>
       <c r="N409" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O409" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="R409" t="n">
-        <v>2.476566156113709</v>
+        <v>2.494255914371664</v>
       </c>
       <c r="S409" t="inlineStr">
         <is>
@@ -74727,10 +74727,10 @@
         </is>
       </c>
       <c r="N410" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="O410" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="U410" t="inlineStr">
         <is>
@@ -78540,13 +78540,13 @@
         </is>
       </c>
       <c r="N432" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O432" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R432" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.2668213756296206</v>
       </c>
       <c r="S432" t="inlineStr">
         <is>
@@ -78704,10 +78704,10 @@
         </is>
       </c>
       <c r="N433" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="O433" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U433" t="inlineStr">
         <is>
@@ -79088,13 +79088,13 @@
         </is>
       </c>
       <c r="N435" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="O435" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="R435" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.583762022512517</v>
       </c>
       <c r="S435" t="inlineStr">
         <is>
@@ -79252,10 +79252,10 @@
         </is>
       </c>
       <c r="N436" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="O436" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="U436" t="inlineStr">
         <is>
@@ -79602,7 +79602,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29375</v>
+        <v>29412</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -73976,12 +73976,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -74015,100 +74015,84 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>63</v>
+        <v>453</v>
       </c>
       <c r="O406" t="n">
-        <v>63</v>
+        <v>453</v>
+      </c>
+      <c r="Q406" t="n">
+        <v>0</v>
       </c>
       <c r="R406" t="n">
-        <v>1.120649777644407</v>
+        <v>0.03206139734093252</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="AA406" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO406" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP406" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ406" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR406" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS406" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS406" t="inlineStr"/>
       <c r="AT406" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU406" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV406" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW406" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX406" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY406" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ406" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA406" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB406" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC406" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -74135,7 +74119,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -74184,98 +74168,23 @@
       <c r="O407" t="n">
         <v>63</v>
       </c>
+      <c r="R407" t="n">
+        <v>1.120649777644407</v>
+      </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U407" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
-      <c r="V407" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="W407" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X407" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y407" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z407" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA407" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB407" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC407" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD407" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE407" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF407" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG407" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH407" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI407" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ407" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK407" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
-        </is>
-      </c>
-      <c r="AM407" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN407" t="b">
-        <v>1</v>
       </c>
       <c r="AO407" t="inlineStr">
         <is>
@@ -74374,17 +74283,17 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -74418,81 +74327,175 @@
         </is>
       </c>
       <c r="N408" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="O408" t="n">
-        <v>46</v>
-      </c>
-      <c r="R408" t="n">
-        <v>0.0891466164944341</v>
-      </c>
-      <c r="S408" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>63</v>
+      </c>
+      <c r="U408" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="W408" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X408" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y408" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z408" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA408" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB408" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC408" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD408" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE408" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF408" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG408" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH408" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI408" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ408" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK408" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
+        </is>
+      </c>
+      <c r="AM408" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN408" t="b">
+        <v>1</v>
       </c>
       <c r="AO408" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP408" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ408" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR408" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS408" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS408" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
       <c r="AT408" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU408" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV408" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW408" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX408" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY408" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ408" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA408" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB408" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC408" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -74524,12 +74527,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -74563,100 +74566,81 @@
         </is>
       </c>
       <c r="N409" t="n">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="O409" t="n">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="R409" t="n">
-        <v>2.494255914371664</v>
+        <v>0.0891466164944341</v>
       </c>
       <c r="S409" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA409" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO409" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP409" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ409" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR409" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS409" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS409" t="inlineStr"/>
       <c r="AT409" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU409" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV409" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW409" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX409" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY409" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ409" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA409" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB409" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC409" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -74683,7 +74667,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -74732,98 +74716,23 @@
       <c r="O410" t="n">
         <v>141</v>
       </c>
+      <c r="R410" t="n">
+        <v>2.494255914371664</v>
+      </c>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U410" t="inlineStr">
         <is>
           <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
-      <c r="V410" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W410" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X410" t="inlineStr">
-        <is>
-          <t>Kikhoste</t>
-        </is>
-      </c>
-      <c r="Y410" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z410" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA410" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB410" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC410" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD410" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE410" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF410" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG410" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH410" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI410" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ410" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK410" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM410" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN410" t="b">
-        <v>1</v>
       </c>
       <c r="AO410" t="inlineStr">
         <is>
@@ -74922,17 +74831,17 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -74966,22 +74875,39 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>22</v>
+        <v>141</v>
       </c>
       <c r="O411" t="n">
-        <v>22</v>
-      </c>
-      <c r="R411" t="n">
-        <v>0.2055873694222336</v>
-      </c>
-      <c r="S411" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>141</v>
       </c>
       <c r="U411" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W411" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X411" t="inlineStr">
+        <is>
+          <t>Kikhoste</t>
+        </is>
+      </c>
+      <c r="Y411" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z411" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA411" t="inlineStr">
@@ -74989,6 +74915,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB411" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC411" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD411" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE411" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF411" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG411" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH411" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI411" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ411" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK411" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM411" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN411" t="b">
+        <v>1</v>
+      </c>
       <c r="AO411" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -75011,7 +74995,7 @@
       </c>
       <c r="AS411" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
       <c r="AT411" t="n">
@@ -75024,42 +75008,42 @@
       </c>
       <c r="AV411" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW411" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX411" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY411" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ411" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA411" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB411" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC411" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -75086,7 +75070,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -75135,98 +75119,23 @@
       <c r="O412" t="n">
         <v>22</v>
       </c>
+      <c r="R412" t="n">
+        <v>0.2055873694222336</v>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U412" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
         </is>
       </c>
-      <c r="V412" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W412" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X412" t="inlineStr">
-        <is>
-          <t>Kikhosta</t>
-        </is>
-      </c>
-      <c r="Y412" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z412" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA412" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB412" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC412" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD412" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE412" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF412" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG412" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH412" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI412" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ412" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK412" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM412" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN412" t="b">
-        <v>1</v>
       </c>
       <c r="AO412" t="inlineStr">
         <is>
@@ -75325,17 +75234,17 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -75369,81 +75278,175 @@
         </is>
       </c>
       <c r="N413" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="O413" t="n">
-        <v>74</v>
-      </c>
-      <c r="R413" t="n">
-        <v>0.02120128218249345</v>
-      </c>
-      <c r="S413" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W413" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X413" t="inlineStr">
+        <is>
+          <t>Kikhosta</t>
+        </is>
+      </c>
+      <c r="Y413" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z413" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB413" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC413" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD413" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE413" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF413" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG413" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH413" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI413" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ413" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK413" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM413" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN413" t="b">
+        <v>1</v>
       </c>
       <c r="AO413" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP413" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ413" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR413" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS413" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS413" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT413" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU413" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV413" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW413" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX413" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY413" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ413" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA413" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB413" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC413" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -75475,12 +75478,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -75505,7 +75508,7 @@
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M414" t="inlineStr">
@@ -75514,13 +75517,13 @@
         </is>
       </c>
       <c r="N414" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="O414" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="R414" t="n">
-        <v>0.05717658852960364</v>
+        <v>0.02120128218249345</v>
       </c>
       <c r="S414" t="inlineStr">
         <is>
@@ -75553,42 +75556,42 @@
       </c>
       <c r="AV414" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW414" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX414" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY414" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ414" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA414" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB414" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC414" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -75620,12 +75623,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -75659,93 +75662,81 @@
         </is>
       </c>
       <c r="N415" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="O415" t="n">
-        <v>2</v>
-      </c>
-      <c r="P415" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="R415" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.05717658852960364</v>
       </c>
       <c r="S415" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA415" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO415" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP415" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ415" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS415" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR415" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS415" t="inlineStr"/>
       <c r="AT415" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU415" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV415" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW415" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX415" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY415" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ415" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA415" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB415" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC415" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -75772,7 +75763,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -75824,98 +75815,18 @@
       <c r="P416" t="n">
         <v>2</v>
       </c>
-      <c r="U416" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V416" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W416" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X416" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y416" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z416" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R416" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA416" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB416" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC416" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD416" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE416" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF416" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG416" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH416" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI416" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ416" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK416" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM416" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN416" t="b">
-        <v>1</v>
       </c>
       <c r="AO416" t="inlineStr">
         <is>
@@ -76009,17 +75920,17 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -76044,7 +75955,7 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
@@ -76053,81 +75964,173 @@
         </is>
       </c>
       <c r="N417" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="O417" t="n">
-        <v>67</v>
-      </c>
-      <c r="R417" t="n">
-        <v>0.01919575548955488</v>
-      </c>
-      <c r="S417" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P417" t="n">
+        <v>2</v>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W417" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X417" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y417" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z417" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA417" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB417" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC417" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD417" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE417" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF417" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG417" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH417" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI417" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ417" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK417" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM417" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN417" t="b">
+        <v>1</v>
       </c>
       <c r="AO417" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP417" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR417" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS417" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ417" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS417" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT417" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU417" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV417" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW417" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX417" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY417" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ417" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA417" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB417" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC417" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -76159,12 +76162,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -76189,7 +76192,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
@@ -76198,13 +76201,13 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="O418" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="R418" t="n">
-        <v>0.06207743897499823</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S418" t="inlineStr">
         <is>
@@ -76237,42 +76240,42 @@
       </c>
       <c r="AV418" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW418" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX418" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY418" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ418" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA418" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB418" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC418" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -76304,12 +76307,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -76343,93 +76346,81 @@
         </is>
       </c>
       <c r="N419" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="O419" t="n">
-        <v>2</v>
-      </c>
-      <c r="P419" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="R419" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.06207743897499823</v>
       </c>
       <c r="S419" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA419" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO419" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP419" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ419" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS419" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR419" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS419" t="inlineStr"/>
       <c r="AT419" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU419" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV419" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW419" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX419" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY419" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ419" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA419" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB419" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC419" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -76456,7 +76447,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -76508,98 +76499,18 @@
       <c r="P420" t="n">
         <v>2</v>
       </c>
-      <c r="U420" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V420" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W420" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X420" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y420" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z420" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R420" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA420" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB420" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC420" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD420" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE420" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF420" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG420" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH420" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI420" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ420" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK420" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM420" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN420" t="b">
-        <v>1</v>
       </c>
       <c r="AO420" t="inlineStr">
         <is>
@@ -76693,17 +76604,17 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -76728,7 +76639,7 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
@@ -76737,81 +76648,173 @@
         </is>
       </c>
       <c r="N421" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="O421" t="n">
-        <v>65</v>
-      </c>
-      <c r="R421" t="n">
-        <v>0.018622747863001</v>
-      </c>
-      <c r="S421" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P421" t="n">
+        <v>2</v>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W421" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X421" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y421" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z421" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA421" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB421" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC421" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD421" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE421" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF421" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG421" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH421" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI421" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ421" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK421" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM421" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN421" t="b">
+        <v>1</v>
       </c>
       <c r="AO421" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP421" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR421" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS421" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ421" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS421" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT421" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU421" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV421" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW421" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX421" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY421" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ421" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA421" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB421" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC421" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -76843,12 +76846,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -76873,7 +76876,7 @@
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M422" t="inlineStr">
@@ -76882,13 +76885,13 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="O422" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="R422" t="n">
-        <v>0.02287063541184146</v>
+        <v>0.018622747863001</v>
       </c>
       <c r="S422" t="inlineStr">
         <is>
@@ -76921,42 +76924,42 @@
       </c>
       <c r="AV422" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW422" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX422" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY422" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ422" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA422" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB422" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC422" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -76988,12 +76991,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -77027,93 +77030,81 @@
         </is>
       </c>
       <c r="N423" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="O423" t="n">
-        <v>3</v>
-      </c>
-      <c r="P423" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="R423" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.02287063541184146</v>
       </c>
       <c r="S423" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA423" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO423" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP423" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ423" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS423" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR423" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS423" t="inlineStr"/>
       <c r="AT423" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU423" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV423" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW423" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX423" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY423" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ423" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA423" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB423" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC423" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -77140,7 +77131,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -77192,98 +77183,18 @@
       <c r="P424" t="n">
         <v>3</v>
       </c>
-      <c r="U424" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V424" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W424" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X424" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y424" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z424" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R424" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA424" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB424" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC424" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD424" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE424" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF424" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG424" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH424" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI424" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ424" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK424" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM424" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN424" t="b">
-        <v>1</v>
       </c>
       <c r="AO424" t="inlineStr">
         <is>
@@ -77377,17 +77288,17 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -77412,7 +77323,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
@@ -77421,81 +77332,173 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="O425" t="n">
-        <v>80</v>
-      </c>
-      <c r="R425" t="n">
-        <v>0.02292030506215508</v>
-      </c>
-      <c r="S425" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P425" t="n">
+        <v>3</v>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V425" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W425" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X425" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y425" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z425" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA425" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB425" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC425" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD425" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE425" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF425" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG425" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH425" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI425" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ425" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK425" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM425" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN425" t="b">
+        <v>1</v>
       </c>
       <c r="AO425" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP425" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR425" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS425" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ425" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS425" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT425" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU425" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV425" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW425" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX425" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY425" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ425" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA425" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB425" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC425" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -77527,12 +77530,12 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -77557,7 +77560,7 @@
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
@@ -77566,13 +77569,13 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="O426" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="R426" t="n">
-        <v>0.05390935489934058</v>
+        <v>0.02292030506215508</v>
       </c>
       <c r="S426" t="inlineStr">
         <is>
@@ -77605,42 +77608,42 @@
       </c>
       <c r="AV426" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW426" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX426" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY426" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ426" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA426" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB426" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC426" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -77672,12 +77675,12 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -77711,93 +77714,81 @@
         </is>
       </c>
       <c r="N427" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="O427" t="n">
-        <v>2</v>
-      </c>
-      <c r="P427" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="R427" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.05390935489934058</v>
       </c>
       <c r="S427" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA427" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO427" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP427" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ427" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS427" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR427" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS427" t="inlineStr"/>
       <c r="AT427" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU427" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV427" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW427" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX427" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY427" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ427" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA427" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB427" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC427" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -77824,7 +77815,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -77876,98 +77867,18 @@
       <c r="P428" t="n">
         <v>2</v>
       </c>
-      <c r="U428" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V428" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W428" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X428" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y428" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z428" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R428" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA428" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB428" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC428" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD428" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE428" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF428" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG428" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH428" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI428" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ428" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK428" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM428" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN428" t="b">
-        <v>1</v>
       </c>
       <c r="AO428" t="inlineStr">
         <is>
@@ -78061,17 +77972,17 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -78096,7 +78007,7 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
@@ -78105,81 +78016,173 @@
         </is>
       </c>
       <c r="N429" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="O429" t="n">
-        <v>67</v>
-      </c>
-      <c r="R429" t="n">
-        <v>0.01919575548955488</v>
-      </c>
-      <c r="S429" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P429" t="n">
+        <v>2</v>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V429" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W429" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X429" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y429" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z429" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA429" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB429" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC429" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD429" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE429" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF429" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG429" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH429" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI429" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ429" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK429" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM429" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN429" t="b">
+        <v>1</v>
       </c>
       <c r="AO429" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP429" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR429" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS429" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ429" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS429" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT429" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU429" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV429" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW429" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX429" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY429" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ429" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA429" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB429" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC429" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -78211,12 +78214,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -78241,7 +78244,7 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
@@ -78250,13 +78253,13 @@
         </is>
       </c>
       <c r="N430" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="O430" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="R430" t="n">
-        <v>0.04329084560098561</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S430" t="inlineStr">
         <is>
@@ -78289,42 +78292,42 @@
       </c>
       <c r="AV430" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW430" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX430" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY430" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ430" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA430" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB430" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC430" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -78356,12 +78359,12 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -78386,22 +78389,22 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N431" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="O431" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="R431" t="n">
-        <v>0.2864793219225436</v>
+        <v>0.04329084560098561</v>
       </c>
       <c r="S431" t="inlineStr">
         <is>
@@ -78434,42 +78437,42 @@
       </c>
       <c r="AV431" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW431" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX431" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY431" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ431" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA431" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB431" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC431" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -78501,12 +78504,12 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -78531,36 +78534,34 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N432" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O432" t="n">
-        <v>15</v>
+        <v>2</v>
+      </c>
+      <c r="P432" t="n">
+        <v>2</v>
       </c>
       <c r="R432" t="n">
-        <v>0.2668213756296206</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S432" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
       <c r="AA432" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO432" t="inlineStr">
@@ -78570,22 +78571,17 @@
       </c>
       <c r="AP432" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ432" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR432" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS432" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_500</t>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
         </is>
       </c>
       <c r="AT432" t="n">
@@ -78593,47 +78589,47 @@
       </c>
       <c r="AU432" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV432" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW432" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX432" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY432" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ432" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA432" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB432" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC432" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -78665,12 +78661,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -78695,33 +78691,36 @@
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N433" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O433" t="n">
-        <v>15</v>
+        <v>2</v>
+      </c>
+      <c r="P433" t="n">
+        <v>2</v>
       </c>
       <c r="U433" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_500</t>
+          <t>SER_SG_CDA_PERTUSSIS</t>
         </is>
       </c>
       <c r="V433" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_500</t>
+          <t>SER_SG_CDA_PERTUSSIS</t>
         </is>
       </c>
       <c r="W433" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X433" t="inlineStr">
@@ -78736,12 +78735,12 @@
       </c>
       <c r="Z433" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA433" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB433" t="inlineStr">
@@ -78751,7 +78750,7 @@
       </c>
       <c r="AC433" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD433" t="inlineStr">
@@ -78786,12 +78785,12 @@
       </c>
       <c r="AJ433" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK433" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM433" t="inlineStr">
@@ -78809,22 +78808,17 @@
       </c>
       <c r="AP433" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ433" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR433" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS433" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_500</t>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
         </is>
       </c>
       <c r="AT433" t="n">
@@ -78832,47 +78826,47 @@
       </c>
       <c r="AU433" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV433" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW433" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ433" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA433" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB433" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC433" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -78904,12 +78898,12 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -78943,13 +78937,13 @@
         </is>
       </c>
       <c r="N434" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="O434" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="R434" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.2864793219225436</v>
       </c>
       <c r="S434" t="inlineStr">
         <is>
@@ -78982,42 +78976,42 @@
       </c>
       <c r="AV434" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW434" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX434" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY434" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ434" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA434" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB434" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC434" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -79049,12 +79043,12 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -79088,13 +79082,13 @@
         </is>
       </c>
       <c r="N435" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="O435" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="R435" t="n">
-        <v>0.583762022512517</v>
+        <v>0.3735499258814688</v>
       </c>
       <c r="S435" t="inlineStr">
         <is>
@@ -79103,7 +79097,7 @@
       </c>
       <c r="U435" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
+          <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
       <c r="AA435" t="inlineStr">
@@ -79123,7 +79117,7 @@
       </c>
       <c r="AQ435" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR435" t="inlineStr">
@@ -79133,7 +79127,7 @@
       </c>
       <c r="AS435" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
+          <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
       <c r="AT435" t="n">
@@ -79141,47 +79135,47 @@
       </c>
       <c r="AU435" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV435" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW435" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX435" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY435" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ435" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA435" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB435" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC435" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -79213,12 +79207,12 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -79252,29 +79246,29 @@
         </is>
       </c>
       <c r="N436" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="O436" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="U436" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
+          <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
       <c r="V436" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
+          <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
       <c r="W436" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X436" t="inlineStr">
         <is>
-          <t>Kikhoste</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="Y436" t="inlineStr">
@@ -79299,7 +79293,7 @@
       </c>
       <c r="AC436" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD436" t="inlineStr">
@@ -79334,17 +79328,17 @@
       </c>
       <c r="AJ436" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK436" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
         </is>
       </c>
       <c r="AM436" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN436" t="b">
@@ -79362,7 +79356,7 @@
       </c>
       <c r="AQ436" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR436" t="inlineStr">
@@ -79372,7 +79366,7 @@
       </c>
       <c r="AS436" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
+          <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
       <c r="AT436" t="n">
@@ -79380,47 +79374,740 @@
       </c>
       <c r="AU436" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV436" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW436" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX436" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY436" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA436" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB436" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC436" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N437" t="n">
+        <v>2</v>
+      </c>
+      <c r="O437" t="n">
+        <v>2</v>
+      </c>
+      <c r="R437" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO437" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP437" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR437" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS437" t="inlineStr"/>
+      <c r="AT437" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU437" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV437" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW437" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX437" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY437" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ437" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA437" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB437" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC437" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N438" t="n">
+        <v>33</v>
+      </c>
+      <c r="O438" t="n">
+        <v>33</v>
+      </c>
+      <c r="R438" t="n">
+        <v>0.583762022512517</v>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA438" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO438" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP438" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ438" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR438" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS438" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT438" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU438" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV436" t="inlineStr">
+      <c r="AV438" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW436" t="inlineStr">
+      <c r="AW438" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX436" t="inlineStr">
+      <c r="AX438" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY436" t="inlineStr">
+      <c r="AY438" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ436" t="inlineStr">
+      <c r="AZ438" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA436" t="inlineStr">
+      <c r="BA438" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB436" t="inlineStr">
+      <c r="BB438" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC436" t="inlineStr">
+      <c r="BC438" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N439" t="n">
+        <v>33</v>
+      </c>
+      <c r="O439" t="n">
+        <v>33</v>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W439" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X439" t="inlineStr">
+        <is>
+          <t>Kikhoste</t>
+        </is>
+      </c>
+      <c r="Y439" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z439" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA439" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB439" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC439" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD439" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE439" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF439" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG439" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH439" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI439" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ439" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK439" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM439" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN439" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO439" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP439" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ439" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR439" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS439" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT439" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU439" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV439" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW439" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX439" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY439" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ439" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA439" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB439" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC439" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N440" t="n">
+        <v>72</v>
+      </c>
+      <c r="O440" t="n">
+        <v>72</v>
+      </c>
+      <c r="R440" t="n">
+        <v>0.02062827455593957</v>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO440" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP440" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR440" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS440" t="inlineStr"/>
+      <c r="AT440" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU440" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV440" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW440" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX440" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY440" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ440" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA440" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB440" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC440" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -79457,7 +80144,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -79540,7 +80227,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -79550,7 +80237,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11">
@@ -79570,7 +80257,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13">
@@ -79602,7 +80289,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29412</v>
+        <v>29945</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -73121,13 +73121,13 @@
         </is>
       </c>
       <c r="N399" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="O399" t="n">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="R399" t="n">
-        <v>3.959291141442334</v>
+        <v>3.966636765081373</v>
       </c>
       <c r="S399" t="inlineStr">
         <is>
@@ -79472,13 +79472,13 @@
         </is>
       </c>
       <c r="N437" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O437" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R437" t="n">
-        <v>0.3735499258814688</v>
+        <v>0.4447022927160344</v>
       </c>
       <c r="S437" t="inlineStr">
         <is>
@@ -79636,10 +79636,10 @@
         </is>
       </c>
       <c r="N438" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="O438" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="U438" t="inlineStr">
         <is>
@@ -80679,7 +80679,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29959</v>
+        <v>29965</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -73121,13 +73121,13 @@
         </is>
       </c>
       <c r="N399" t="n">
-        <v>1080</v>
+        <v>1092</v>
       </c>
       <c r="O399" t="n">
-        <v>1080</v>
+        <v>1092</v>
       </c>
       <c r="R399" t="n">
-        <v>3.966636765081373</v>
+        <v>4.01071050691561</v>
       </c>
       <c r="S399" t="inlineStr">
         <is>
@@ -80679,7 +80679,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29965</v>
+        <v>29977</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -79472,13 +79472,13 @@
         </is>
       </c>
       <c r="N437" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="O437" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R437" t="n">
-        <v>0.4447022927160344</v>
+        <v>0.5336427512592412</v>
       </c>
       <c r="S437" t="inlineStr">
         <is>
@@ -79636,10 +79636,10 @@
         </is>
       </c>
       <c r="N438" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="O438" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="U438" t="inlineStr">
         <is>
@@ -79875,13 +79875,13 @@
         </is>
       </c>
       <c r="N439" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O439" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R439" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S439" t="inlineStr">
         <is>
@@ -80498,6 +80498,151 @@
       <c r="BC442" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N443" t="n">
+        <v>46</v>
+      </c>
+      <c r="O443" t="n">
+        <v>46</v>
+      </c>
+      <c r="R443" t="n">
+        <v>0.03757318674802525</v>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO443" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP443" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR443" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS443" t="inlineStr"/>
+      <c r="AT443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU443" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV443" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW443" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX443" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY443" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA443" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB443" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC443" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -80534,7 +80679,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -80617,7 +80762,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -80627,7 +80772,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="11">
@@ -80679,7 +80824,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29977</v>
+        <v>30030</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -69444,13 +69444,13 @@
         </is>
       </c>
       <c r="N378" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O378" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R378" t="n">
-        <v>2.98819153702549</v>
+        <v>2.969278932360772</v>
       </c>
       <c r="S378" t="inlineStr">
         <is>
@@ -69603,10 +69603,10 @@
         </is>
       </c>
       <c r="N379" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O379" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="U379" t="inlineStr">
         <is>
@@ -75465,12 +75465,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -75504,13 +75504,13 @@
         </is>
       </c>
       <c r="N414" t="n">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="O414" t="n">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="R414" t="n">
-        <v>0.2055873694222336</v>
+        <v>2.723415071719434</v>
       </c>
       <c r="S414" t="inlineStr">
         <is>
@@ -75519,7 +75519,7 @@
       </c>
       <c r="U414" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA414" t="inlineStr">
@@ -75534,7 +75534,7 @@
       </c>
       <c r="AP414" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ414" t="inlineStr">
@@ -75542,62 +75542,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR414" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS414" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT414" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU414" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV414" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW414" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX414" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY414" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ414" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA414" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB414" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC414" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -75629,12 +75624,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -75668,29 +75663,29 @@
         </is>
       </c>
       <c r="N415" t="n">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="O415" t="n">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="U415" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V415" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W415" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X415" t="inlineStr">
         <is>
-          <t>Kikhosta</t>
+          <t>Pertussis</t>
         </is>
       </c>
       <c r="Y415" t="inlineStr">
@@ -75700,7 +75695,7 @@
       </c>
       <c r="Z415" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA415" t="inlineStr">
@@ -75715,7 +75710,7 @@
       </c>
       <c r="AC415" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD415" t="inlineStr">
@@ -75750,17 +75745,17 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly pertussis notifications.</t>
         </is>
       </c>
       <c r="AM415" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN415" t="b">
@@ -75773,7 +75768,7 @@
       </c>
       <c r="AP415" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ415" t="inlineStr">
@@ -75781,62 +75776,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR415" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS415" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT415" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU415" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV415" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW415" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX415" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY415" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ415" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA415" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB415" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC415" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -75868,12 +75858,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -75907,81 +75897,100 @@
         </is>
       </c>
       <c r="N416" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="O416" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="R416" t="n">
-        <v>0.02120128218249345</v>
+        <v>0.2055873694222336</v>
       </c>
       <c r="S416" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="AA416" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO416" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP416" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ416" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR416" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS416" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS416" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT416" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU416" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV416" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW416" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX416" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY416" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ416" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA416" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB416" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC416" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -76008,17 +76017,17 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -76043,7 +76052,7 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
@@ -76052,81 +76061,175 @@
         </is>
       </c>
       <c r="N417" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="O417" t="n">
-        <v>70</v>
-      </c>
-      <c r="R417" t="n">
-        <v>0.05717658852960364</v>
-      </c>
-      <c r="S417" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="U417" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W417" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X417" t="inlineStr">
+        <is>
+          <t>Kikhosta</t>
+        </is>
+      </c>
+      <c r="Y417" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z417" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA417" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB417" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC417" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD417" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE417" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF417" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG417" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH417" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI417" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ417" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK417" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM417" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN417" t="b">
+        <v>1</v>
       </c>
       <c r="AO417" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP417" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ417" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR417" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS417" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS417" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT417" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU417" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV417" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW417" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX417" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY417" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ417" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA417" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB417" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC417" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -76158,12 +76261,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -76188,7 +76291,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
@@ -76197,93 +76300,81 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="O418" t="n">
-        <v>2</v>
-      </c>
-      <c r="P418" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="R418" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.02120128218249345</v>
       </c>
       <c r="S418" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA418" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO418" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP418" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ418" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS418" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR418" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS418" t="inlineStr"/>
       <c r="AT418" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU418" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV418" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW418" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX418" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY418" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ418" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA418" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB418" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC418" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -76310,17 +76401,17 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -76354,173 +76445,81 @@
         </is>
       </c>
       <c r="N419" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="O419" t="n">
-        <v>2</v>
-      </c>
-      <c r="P419" t="n">
-        <v>2</v>
-      </c>
-      <c r="U419" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V419" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W419" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X419" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y419" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z419" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA419" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB419" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC419" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD419" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE419" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF419" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG419" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH419" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI419" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ419" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK419" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM419" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN419" t="b">
-        <v>1</v>
+        <v>70</v>
+      </c>
+      <c r="R419" t="n">
+        <v>0.05717658852960364</v>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO419" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP419" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ419" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS419" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR419" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS419" t="inlineStr"/>
       <c r="AT419" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU419" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV419" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW419" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX419" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY419" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ419" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA419" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB419" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC419" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -76552,12 +76551,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -76582,7 +76581,7 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
@@ -76591,81 +76590,93 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="O420" t="n">
-        <v>67</v>
+        <v>2</v>
+      </c>
+      <c r="P420" t="n">
+        <v>2</v>
       </c>
       <c r="R420" t="n">
-        <v>0.01919575548955488</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S420" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA420" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO420" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP420" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR420" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS420" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ420" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS420" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT420" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU420" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV420" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW420" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX420" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY420" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ420" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA420" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB420" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC420" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -76692,17 +76703,17 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -76727,7 +76738,7 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
@@ -76736,81 +76747,173 @@
         </is>
       </c>
       <c r="N421" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="O421" t="n">
-        <v>76</v>
-      </c>
-      <c r="R421" t="n">
-        <v>0.06207743897499823</v>
-      </c>
-      <c r="S421" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P421" t="n">
+        <v>2</v>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W421" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X421" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y421" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z421" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA421" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB421" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC421" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD421" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE421" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF421" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG421" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH421" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI421" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ421" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK421" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM421" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN421" t="b">
+        <v>1</v>
       </c>
       <c r="AO421" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP421" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR421" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS421" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ421" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS421" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT421" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU421" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV421" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW421" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX421" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY421" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ421" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA421" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB421" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC421" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -76842,12 +76945,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -76872,7 +76975,7 @@
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M422" t="inlineStr">
@@ -76881,93 +76984,81 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="O422" t="n">
-        <v>2</v>
-      </c>
-      <c r="P422" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="R422" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S422" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA422" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO422" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP422" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ422" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS422" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR422" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS422" t="inlineStr"/>
       <c r="AT422" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU422" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV422" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW422" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX422" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY422" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ422" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA422" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB422" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC422" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -76994,17 +77085,17 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -77038,173 +77129,81 @@
         </is>
       </c>
       <c r="N423" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="O423" t="n">
-        <v>2</v>
-      </c>
-      <c r="P423" t="n">
-        <v>2</v>
-      </c>
-      <c r="U423" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V423" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W423" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X423" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y423" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z423" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA423" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB423" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC423" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD423" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE423" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF423" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG423" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH423" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI423" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ423" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK423" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM423" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN423" t="b">
-        <v>1</v>
+        <v>76</v>
+      </c>
+      <c r="R423" t="n">
+        <v>0.06207743897499823</v>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO423" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP423" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ423" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS423" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR423" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS423" t="inlineStr"/>
       <c r="AT423" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU423" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV423" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW423" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX423" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY423" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ423" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA423" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB423" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC423" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -77236,12 +77235,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -77266,7 +77265,7 @@
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
@@ -77275,81 +77274,93 @@
         </is>
       </c>
       <c r="N424" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="O424" t="n">
-        <v>65</v>
+        <v>2</v>
+      </c>
+      <c r="P424" t="n">
+        <v>2</v>
       </c>
       <c r="R424" t="n">
-        <v>0.018622747863001</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA424" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO424" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP424" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR424" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS424" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ424" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS424" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT424" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU424" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV424" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW424" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX424" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY424" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ424" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA424" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB424" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC424" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -77376,17 +77387,17 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -77411,7 +77422,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
@@ -77420,81 +77431,173 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="O425" t="n">
-        <v>28</v>
-      </c>
-      <c r="R425" t="n">
-        <v>0.02287063541184146</v>
-      </c>
-      <c r="S425" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P425" t="n">
+        <v>2</v>
+      </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V425" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W425" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X425" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y425" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z425" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA425" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB425" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC425" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD425" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE425" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF425" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG425" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH425" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI425" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ425" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK425" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM425" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN425" t="b">
+        <v>1</v>
       </c>
       <c r="AO425" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP425" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR425" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS425" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ425" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS425" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT425" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU425" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV425" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW425" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX425" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY425" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ425" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA425" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB425" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC425" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -77526,12 +77629,12 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -77556,7 +77659,7 @@
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
@@ -77565,93 +77668,81 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="O426" t="n">
-        <v>3</v>
-      </c>
-      <c r="P426" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="R426" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.018622747863001</v>
       </c>
       <c r="S426" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA426" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO426" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP426" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ426" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS426" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR426" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS426" t="inlineStr"/>
       <c r="AT426" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU426" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV426" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW426" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX426" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY426" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ426" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA426" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB426" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC426" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -77678,17 +77769,17 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -77722,173 +77813,81 @@
         </is>
       </c>
       <c r="N427" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="O427" t="n">
-        <v>3</v>
-      </c>
-      <c r="P427" t="n">
-        <v>3</v>
-      </c>
-      <c r="U427" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V427" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W427" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X427" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y427" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z427" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA427" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB427" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC427" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD427" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE427" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF427" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG427" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH427" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI427" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ427" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK427" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM427" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN427" t="b">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="R427" t="n">
+        <v>0.02287063541184146</v>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO427" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP427" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ427" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS427" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR427" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS427" t="inlineStr"/>
       <c r="AT427" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU427" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV427" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW427" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX427" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY427" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ427" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA427" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB427" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC427" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -77920,12 +77919,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -77950,7 +77949,7 @@
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
@@ -77959,81 +77958,93 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="O428" t="n">
-        <v>80</v>
+        <v>3</v>
+      </c>
+      <c r="P428" t="n">
+        <v>3</v>
       </c>
       <c r="R428" t="n">
-        <v>0.02292030506215508</v>
+        <v>0.05079797265291142</v>
       </c>
       <c r="S428" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA428" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO428" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP428" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR428" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS428" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ428" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS428" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT428" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU428" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV428" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW428" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX428" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY428" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ428" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA428" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB428" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC428" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -78060,17 +78071,17 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -78095,7 +78106,7 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
@@ -78104,81 +78115,173 @@
         </is>
       </c>
       <c r="N429" t="n">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="O429" t="n">
-        <v>66</v>
-      </c>
-      <c r="R429" t="n">
-        <v>0.05390935489934058</v>
-      </c>
-      <c r="S429" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P429" t="n">
+        <v>3</v>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V429" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W429" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X429" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y429" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z429" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA429" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB429" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC429" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD429" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE429" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF429" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG429" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH429" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI429" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ429" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK429" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM429" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN429" t="b">
+        <v>1</v>
       </c>
       <c r="AO429" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP429" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR429" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS429" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ429" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS429" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT429" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU429" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV429" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW429" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX429" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY429" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ429" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA429" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB429" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC429" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -78210,12 +78313,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -78240,7 +78343,7 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
@@ -78249,93 +78352,81 @@
         </is>
       </c>
       <c r="N430" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="O430" t="n">
-        <v>2</v>
-      </c>
-      <c r="P430" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="R430" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.02292030506215508</v>
       </c>
       <c r="S430" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA430" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO430" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP430" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ430" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS430" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR430" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS430" t="inlineStr"/>
       <c r="AT430" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU430" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV430" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW430" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX430" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY430" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ430" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA430" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB430" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC430" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -78362,17 +78453,17 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -78406,173 +78497,81 @@
         </is>
       </c>
       <c r="N431" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="O431" t="n">
-        <v>2</v>
-      </c>
-      <c r="P431" t="n">
-        <v>2</v>
-      </c>
-      <c r="U431" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V431" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W431" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X431" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y431" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z431" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA431" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB431" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC431" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD431" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE431" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF431" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG431" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH431" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI431" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ431" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK431" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM431" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN431" t="b">
-        <v>1</v>
+        <v>66</v>
+      </c>
+      <c r="R431" t="n">
+        <v>0.05390935489934058</v>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO431" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP431" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ431" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS431" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR431" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS431" t="inlineStr"/>
       <c r="AT431" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU431" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV431" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW431" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX431" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY431" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ431" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA431" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB431" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC431" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -78604,12 +78603,12 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -78634,7 +78633,7 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
@@ -78643,81 +78642,93 @@
         </is>
       </c>
       <c r="N432" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="O432" t="n">
-        <v>67</v>
+        <v>2</v>
+      </c>
+      <c r="P432" t="n">
+        <v>2</v>
       </c>
       <c r="R432" t="n">
-        <v>0.01919575548955488</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S432" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA432" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO432" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP432" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR432" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS432" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ432" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS432" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT432" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU432" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV432" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW432" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX432" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY432" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ432" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA432" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB432" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC432" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -78744,17 +78755,17 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -78779,7 +78790,7 @@
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
@@ -78788,81 +78799,173 @@
         </is>
       </c>
       <c r="N433" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
       <c r="O433" t="n">
-        <v>53</v>
-      </c>
-      <c r="R433" t="n">
-        <v>0.04329084560098561</v>
-      </c>
-      <c r="S433" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P433" t="n">
+        <v>2</v>
+      </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V433" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W433" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X433" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y433" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z433" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA433" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB433" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC433" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD433" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE433" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF433" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG433" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH433" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI433" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ433" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK433" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM433" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN433" t="b">
+        <v>1</v>
       </c>
       <c r="AO433" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP433" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR433" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS433" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ433" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS433" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT433" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU433" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV433" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW433" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ433" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA433" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB433" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC433" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -78894,12 +78997,12 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -78924,7 +79027,7 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
@@ -78933,93 +79036,81 @@
         </is>
       </c>
       <c r="N434" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="O434" t="n">
-        <v>2</v>
-      </c>
-      <c r="P434" t="n">
-        <v>2</v>
+        <v>67</v>
       </c>
       <c r="R434" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S434" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA434" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO434" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP434" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ434" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS434" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR434" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS434" t="inlineStr"/>
       <c r="AT434" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU434" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV434" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW434" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX434" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY434" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ434" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA434" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB434" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC434" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -79046,17 +79137,17 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -79090,173 +79181,81 @@
         </is>
       </c>
       <c r="N435" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="O435" t="n">
-        <v>2</v>
-      </c>
-      <c r="P435" t="n">
-        <v>2</v>
-      </c>
-      <c r="U435" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V435" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W435" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X435" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y435" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z435" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA435" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB435" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC435" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD435" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE435" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF435" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG435" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH435" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI435" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ435" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK435" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM435" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN435" t="b">
-        <v>1</v>
+        <v>53</v>
+      </c>
+      <c r="R435" t="n">
+        <v>0.04329084560098561</v>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO435" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP435" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ435" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS435" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR435" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS435" t="inlineStr"/>
       <c r="AT435" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU435" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV435" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW435" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX435" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY435" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ435" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA435" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB435" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC435" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -79288,12 +79287,12 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -79318,90 +79317,102 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N436" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="O436" t="n">
-        <v>78</v>
+        <v>2</v>
+      </c>
+      <c r="P436" t="n">
+        <v>2</v>
       </c>
       <c r="R436" t="n">
-        <v>0.2864793219225436</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S436" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO436" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP436" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR436" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS436" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ436" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS436" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT436" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU436" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV436" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW436" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX436" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY436" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ436" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA436" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB436" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC436" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -79428,17 +79439,17 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -79463,37 +79474,115 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N437" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="O437" t="n">
-        <v>30</v>
-      </c>
-      <c r="R437" t="n">
-        <v>0.5336427512592412</v>
-      </c>
-      <c r="S437" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P437" t="n">
+        <v>2</v>
       </c>
       <c r="U437" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_500</t>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W437" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X437" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y437" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z437" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA437" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB437" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC437" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD437" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE437" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF437" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG437" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH437" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI437" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ437" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK437" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM437" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN437" t="b">
+        <v>1</v>
       </c>
       <c r="AO437" t="inlineStr">
         <is>
@@ -79502,22 +79591,17 @@
       </c>
       <c r="AP437" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ437" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR437" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS437" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_500</t>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
         </is>
       </c>
       <c r="AT437" t="n">
@@ -79525,47 +79609,47 @@
       </c>
       <c r="AU437" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV437" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW437" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX437" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY437" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ437" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA437" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB437" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC437" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -79592,17 +79676,17 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -79636,175 +79720,81 @@
         </is>
       </c>
       <c r="N438" t="n">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="O438" t="n">
-        <v>30</v>
-      </c>
-      <c r="U438" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="V438" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="W438" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X438" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y438" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z438" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA438" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB438" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC438" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD438" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="R438" t="n">
+        <v>0.2864793219225436</v>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO438" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP438" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR438" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS438" t="inlineStr"/>
+      <c r="AT438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU438" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV438" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE438" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF438" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG438" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH438" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI438" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ438" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK438" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
-        </is>
-      </c>
-      <c r="AM438" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN438" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO438" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP438" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ438" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR438" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS438" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="AT438" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU438" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV438" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW438" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX438" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY438" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ438" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA438" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB438" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC438" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -79836,12 +79826,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -79875,81 +79865,100 @@
         </is>
       </c>
       <c r="N439" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="O439" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="R439" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.5336427512592412</v>
       </c>
       <c r="S439" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="AA439" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO439" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP439" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ439" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR439" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS439" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS439" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
       <c r="AT439" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU439" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV439" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW439" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX439" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY439" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ439" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA439" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB439" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC439" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -79976,17 +79985,17 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -80020,22 +80029,39 @@
         </is>
       </c>
       <c r="N440" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="O440" t="n">
-        <v>33</v>
-      </c>
-      <c r="R440" t="n">
-        <v>0.583762022512517</v>
-      </c>
-      <c r="S440" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>30</v>
       </c>
       <c r="U440" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="W440" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X440" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y440" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z440" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA440" t="inlineStr">
@@ -80043,6 +80069,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB440" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC440" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD440" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE440" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF440" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG440" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH440" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI440" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ440" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK440" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
+        </is>
+      </c>
+      <c r="AM440" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN440" t="b">
+        <v>1</v>
+      </c>
       <c r="AO440" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -80055,7 +80139,7 @@
       </c>
       <c r="AQ440" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR440" t="inlineStr">
@@ -80065,7 +80149,7 @@
       </c>
       <c r="AS440" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
+          <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
       <c r="AT440" t="n">
@@ -80073,47 +80157,47 @@
       </c>
       <c r="AU440" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV440" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW440" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX440" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY440" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ440" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA440" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB440" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC440" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -80140,17 +80224,17 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -80184,175 +80268,81 @@
         </is>
       </c>
       <c r="N441" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="O441" t="n">
-        <v>33</v>
-      </c>
-      <c r="U441" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V441" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W441" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X441" t="inlineStr">
-        <is>
-          <t>Kikhoste</t>
-        </is>
-      </c>
-      <c r="Y441" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z441" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA441" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB441" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC441" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD441" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE441" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF441" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG441" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH441" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI441" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ441" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK441" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM441" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN441" t="b">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="R441" t="n">
+        <v>0.007751879695168184</v>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO441" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP441" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ441" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR441" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS441" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS441" t="inlineStr"/>
       <c r="AT441" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU441" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV441" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW441" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX441" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY441" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ441" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA441" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB441" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC441" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -80384,12 +80374,12 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -80414,7 +80404,7 @@
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
@@ -80423,81 +80413,100 @@
         </is>
       </c>
       <c r="N442" t="n">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="O442" t="n">
-        <v>72</v>
+        <v>33</v>
       </c>
       <c r="R442" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.583762022512517</v>
       </c>
       <c r="S442" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO442" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP442" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ442" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR442" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS442" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS442" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT442" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU442" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV442" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW442" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX442" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY442" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ442" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA442" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB442" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC442" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -80524,123 +80533,507 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N443" t="n">
+        <v>33</v>
+      </c>
+      <c r="O443" t="n">
+        <v>33</v>
+      </c>
+      <c r="U443" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V443" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W443" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X443" t="inlineStr">
+        <is>
+          <t>Kikhoste</t>
+        </is>
+      </c>
+      <c r="Y443" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z443" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA443" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB443" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC443" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD443" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE443" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF443" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG443" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH443" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI443" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ443" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK443" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM443" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN443" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO443" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP443" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ443" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR443" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS443" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT443" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU443" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV443" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW443" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX443" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY443" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA443" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB443" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC443" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F443" t="inlineStr">
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N444" t="n">
+        <v>72</v>
+      </c>
+      <c r="O444" t="n">
+        <v>72</v>
+      </c>
+      <c r="R444" t="n">
+        <v>0.02062827455593957</v>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO444" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP444" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR444" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS444" t="inlineStr"/>
+      <c r="AT444" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU444" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV444" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW444" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX444" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY444" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ444" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA444" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB444" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC444" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G443" t="inlineStr">
+      <c r="G445" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H443" t="inlineStr">
-        <is>
-          <t>D028</t>
-        </is>
-      </c>
-      <c r="I443" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="J443" t="inlineStr">
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
         <is>
           <t>百日咳</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr">
+      <c r="K445" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L443" t="inlineStr">
+      <c r="L445" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M443" t="inlineStr">
+      <c r="M445" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N443" t="n">
+      <c r="N445" t="n">
         <v>46</v>
       </c>
-      <c r="O443" t="n">
+      <c r="O445" t="n">
         <v>46</v>
       </c>
-      <c r="R443" t="n">
+      <c r="R445" t="n">
         <v>0.03757318674802525</v>
       </c>
-      <c r="S443" t="inlineStr">
+      <c r="S445" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO443" t="inlineStr">
+      <c r="AO445" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP443" t="inlineStr">
+      <c r="AP445" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR443" t="inlineStr">
+      <c r="AR445" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS443" t="inlineStr"/>
-      <c r="AT443" t="n">
+      <c r="AS445" t="inlineStr"/>
+      <c r="AT445" t="n">
         <v>0</v>
       </c>
-      <c r="AU443" t="inlineStr">
+      <c r="AU445" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV443" t="inlineStr">
+      <c r="AV445" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW443" t="inlineStr">
+      <c r="AW445" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX443" t="inlineStr">
+      <c r="AX445" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY443" t="inlineStr">
+      <c r="AY445" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ443" t="inlineStr">
+      <c r="AZ445" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA443" t="inlineStr">
+      <c r="BA445" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB443" t="inlineStr">
+      <c r="BB445" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC443" t="inlineStr">
+      <c r="BC445" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -80762,7 +81155,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -80772,7 +81165,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11">
@@ -80792,7 +81185,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -80824,7 +81217,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30030</v>
+        <v>30173</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -80413,13 +80413,13 @@
         </is>
       </c>
       <c r="N442" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="O442" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="R442" t="n">
-        <v>0.583762022512517</v>
+        <v>1.079075253735259</v>
       </c>
       <c r="S442" t="inlineStr">
         <is>
@@ -80577,10 +80577,10 @@
         </is>
       </c>
       <c r="N443" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="O443" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="U443" t="inlineStr">
         <is>
@@ -81217,7 +81217,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30173</v>
+        <v>30201</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -64585,13 +64585,13 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="O352" t="n">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="R352" t="n">
-        <v>0.1390692506641839</v>
+        <v>0.1493706766393086</v>
       </c>
       <c r="S352" t="inlineStr">
         <is>
@@ -74260,13 +74260,13 @@
         </is>
       </c>
       <c r="N407" t="n">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="O407" t="n">
-        <v>41</v>
+        <v>132</v>
       </c>
       <c r="R407" t="n">
-        <v>0.01919811204455063</v>
+        <v>0.06180855585074838</v>
       </c>
       <c r="S407" t="inlineStr">
         <is>
@@ -79826,12 +79826,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -79865,100 +79865,81 @@
         </is>
       </c>
       <c r="N439" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O439" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="R439" t="n">
-        <v>0.5336427512592412</v>
+        <v>0.0004682466352329422</v>
       </c>
       <c r="S439" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="AA439" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO439" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP439" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ439" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR439" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS439" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS439" t="inlineStr"/>
       <c r="AT439" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU439" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV439" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW439" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX439" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY439" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ439" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA439" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB439" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC439" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -79985,7 +79966,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
@@ -80029,103 +80010,28 @@
         </is>
       </c>
       <c r="N440" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O440" t="n">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="R440" t="n">
+        <v>0.569218934676524</v>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U440" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
-      <c r="V440" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="W440" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X440" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y440" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z440" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA440" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB440" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC440" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD440" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE440" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF440" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG440" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH440" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI440" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ440" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK440" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
-        </is>
-      </c>
-      <c r="AM440" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN440" t="b">
-        <v>1</v>
       </c>
       <c r="AO440" t="inlineStr">
         <is>
@@ -80224,17 +80130,17 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -80268,81 +80174,175 @@
         </is>
       </c>
       <c r="N441" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="O441" t="n">
-        <v>4</v>
-      </c>
-      <c r="R441" t="n">
-        <v>0.007751879695168184</v>
-      </c>
-      <c r="S441" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="W441" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X441" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y441" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z441" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA441" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB441" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC441" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD441" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE441" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF441" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG441" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH441" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI441" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ441" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK441" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
+        </is>
+      </c>
+      <c r="AM441" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN441" t="b">
+        <v>1</v>
       </c>
       <c r="AO441" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP441" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ441" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR441" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS441" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS441" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
       <c r="AT441" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU441" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV441" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW441" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX441" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY441" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ441" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA441" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB441" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC441" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -80374,12 +80374,12 @@
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -80413,100 +80413,81 @@
         </is>
       </c>
       <c r="N442" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="O442" t="n">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="R442" t="n">
-        <v>1.079075253735259</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S442" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA442" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO442" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP442" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ442" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR442" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS442" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS442" t="inlineStr"/>
       <c r="AT442" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU442" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV442" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW442" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX442" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY442" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ442" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA442" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB442" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC442" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -80533,7 +80514,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -80582,98 +80563,23 @@
       <c r="O443" t="n">
         <v>61</v>
       </c>
+      <c r="R443" t="n">
+        <v>1.079075253735259</v>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U443" t="inlineStr">
         <is>
           <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
-      <c r="V443" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W443" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X443" t="inlineStr">
-        <is>
-          <t>Kikhoste</t>
-        </is>
-      </c>
-      <c r="Y443" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z443" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA443" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB443" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC443" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD443" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE443" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF443" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG443" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH443" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI443" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ443" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK443" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM443" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN443" t="b">
-        <v>1</v>
       </c>
       <c r="AO443" t="inlineStr">
         <is>
@@ -80772,17 +80678,17 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -80807,7 +80713,7 @@
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M444" t="inlineStr">
@@ -80816,81 +80722,175 @@
         </is>
       </c>
       <c r="N444" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="O444" t="n">
-        <v>72</v>
-      </c>
-      <c r="R444" t="n">
-        <v>0.02062827455593957</v>
-      </c>
-      <c r="S444" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>61</v>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W444" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X444" t="inlineStr">
+        <is>
+          <t>Kikhoste</t>
+        </is>
+      </c>
+      <c r="Y444" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z444" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA444" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB444" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC444" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD444" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE444" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF444" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG444" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH444" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI444" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ444" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK444" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM444" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN444" t="b">
+        <v>1</v>
       </c>
       <c r="AO444" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP444" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ444" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR444" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS444" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS444" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU444" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV444" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW444" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX444" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY444" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ444" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA444" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB444" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC444" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -80922,12 +80922,12 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -80952,7 +80952,7 @@
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M445" t="inlineStr">
@@ -80961,13 +80961,13 @@
         </is>
       </c>
       <c r="N445" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="O445" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="R445" t="n">
-        <v>0.03757318674802525</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S445" t="inlineStr">
         <is>
@@ -81000,40 +81000,185 @@
       </c>
       <c r="AV445" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW445" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX445" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY445" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ445" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA445" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB445" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC445" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N446" t="n">
+        <v>46</v>
+      </c>
+      <c r="O446" t="n">
+        <v>46</v>
+      </c>
+      <c r="R446" t="n">
+        <v>0.03757318674802525</v>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO446" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP446" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR446" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS446" t="inlineStr"/>
+      <c r="AT446" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU446" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV446" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW445" t="inlineStr">
+      <c r="AW446" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX445" t="inlineStr">
+      <c r="AX446" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY445" t="inlineStr">
+      <c r="AY446" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ445" t="inlineStr">
+      <c r="AZ446" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA445" t="inlineStr">
+      <c r="BA446" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB445" t="inlineStr">
+      <c r="BB446" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC445" t="inlineStr">
+      <c r="BC446" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -81155,7 +81300,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -81165,7 +81310,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11">
@@ -81217,7 +81362,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30201</v>
+        <v>30317</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -63304,13 +63304,13 @@
         </is>
       </c>
       <c r="N343" t="n">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="O343" t="n">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="R343" t="n">
-        <v>3.235747212996935</v>
+        <v>3.250438460275014</v>
       </c>
       <c r="S343" t="inlineStr">
         <is>
@@ -73121,13 +73121,13 @@
         </is>
       </c>
       <c r="N399" t="n">
-        <v>1092</v>
+        <v>1102</v>
       </c>
       <c r="O399" t="n">
-        <v>1092</v>
+        <v>1102</v>
       </c>
       <c r="R399" t="n">
-        <v>4.01071050691561</v>
+        <v>4.047438625110809</v>
       </c>
       <c r="S399" t="inlineStr">
         <is>
@@ -80413,13 +80413,13 @@
         </is>
       </c>
       <c r="N442" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O442" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R442" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S442" t="inlineStr">
         <is>
@@ -81181,6 +81181,545 @@
       <c r="BC446" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N447" t="n">
+        <v>2</v>
+      </c>
+      <c r="O447" t="n">
+        <v>2</v>
+      </c>
+      <c r="P447" t="n">
+        <v>2</v>
+      </c>
+      <c r="R447" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO447" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP447" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ447" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS447" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="AT447" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU447" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV447" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW447" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX447" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY447" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ447" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA447" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB447" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC447" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N448" t="n">
+        <v>2</v>
+      </c>
+      <c r="O448" t="n">
+        <v>2</v>
+      </c>
+      <c r="P448" t="n">
+        <v>2</v>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W448" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X448" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y448" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z448" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB448" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC448" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD448" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE448" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF448" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG448" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH448" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI448" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ448" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK448" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM448" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN448" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO448" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP448" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ448" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS448" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="AT448" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU448" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV448" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW448" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX448" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY448" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ448" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA448" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB448" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC448" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N449" t="n">
+        <v>74</v>
+      </c>
+      <c r="O449" t="n">
+        <v>74</v>
+      </c>
+      <c r="R449" t="n">
+        <v>0.02120128218249345</v>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO449" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP449" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR449" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS449" t="inlineStr"/>
+      <c r="AT449" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU449" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV449" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW449" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX449" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY449" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA449" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB449" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC449" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -81217,7 +81756,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -81300,7 +81839,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -81310,7 +81849,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="11">
@@ -81330,7 +81869,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -81362,7 +81901,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30317</v>
+        <v>30410</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -73121,13 +73121,13 @@
         </is>
       </c>
       <c r="N399" t="n">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="O399" t="n">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="R399" t="n">
-        <v>4.047438625110809</v>
+        <v>4.051111436930329</v>
       </c>
       <c r="S399" t="inlineStr">
         <is>
@@ -80413,13 +80413,13 @@
         </is>
       </c>
       <c r="N442" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O442" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R442" t="n">
-        <v>0.01356578946654432</v>
+        <v>0.02713157893308864</v>
       </c>
       <c r="S442" t="inlineStr">
         <is>
@@ -81901,7 +81901,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30410</v>
+        <v>30418</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -64585,13 +64585,13 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="O352" t="n">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="R352" t="n">
-        <v>0.1493706766393086</v>
+        <v>0.1563943761678027</v>
       </c>
       <c r="S352" t="inlineStr">
         <is>
@@ -73121,13 +73121,13 @@
         </is>
       </c>
       <c r="N399" t="n">
-        <v>1103</v>
+        <v>1112</v>
       </c>
       <c r="O399" t="n">
-        <v>1103</v>
+        <v>1112</v>
       </c>
       <c r="R399" t="n">
-        <v>4.051111436930329</v>
+        <v>4.084166743306007</v>
       </c>
       <c r="S399" t="inlineStr">
         <is>
@@ -74260,13 +74260,13 @@
         </is>
       </c>
       <c r="N407" t="n">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="O407" t="n">
-        <v>132</v>
+        <v>237</v>
       </c>
       <c r="R407" t="n">
-        <v>0.06180855585074838</v>
+        <v>0.1109744525502073</v>
       </c>
       <c r="S407" t="inlineStr">
         <is>
@@ -74917,12 +74917,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -74956,13 +74956,13 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="O411" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="R411" t="n">
-        <v>0.0891466164944341</v>
+        <v>0</v>
       </c>
       <c r="S411" t="inlineStr">
         <is>
@@ -74995,42 +74995,42 @@
       </c>
       <c r="AV411" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW411" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX411" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY411" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ411" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA411" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB411" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC411" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -75062,12 +75062,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -75101,100 +75101,81 @@
         </is>
       </c>
       <c r="N412" t="n">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="O412" t="n">
-        <v>141</v>
+        <v>46</v>
       </c>
       <c r="R412" t="n">
-        <v>2.494255914371664</v>
+        <v>0.0891466164944341</v>
       </c>
       <c r="S412" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA412" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO412" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP412" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ412" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR412" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS412" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS412" t="inlineStr"/>
       <c r="AT412" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU412" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV412" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW412" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX412" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY412" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ412" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA412" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB412" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC412" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -75221,7 +75202,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -75265,103 +75246,28 @@
         </is>
       </c>
       <c r="N413" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O413" t="n">
-        <v>141</v>
+        <v>140</v>
+      </c>
+      <c r="R413" t="n">
+        <v>2.476566156113709</v>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U413" t="inlineStr">
         <is>
           <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
-      <c r="V413" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W413" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X413" t="inlineStr">
-        <is>
-          <t>Kikhoste</t>
-        </is>
-      </c>
-      <c r="Y413" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z413" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA413" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB413" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC413" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD413" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE413" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF413" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG413" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH413" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI413" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ413" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK413" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM413" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN413" t="b">
-        <v>1</v>
       </c>
       <c r="AO413" t="inlineStr">
         <is>
@@ -75460,17 +75366,17 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -75504,22 +75410,39 @@
         </is>
       </c>
       <c r="N414" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="O414" t="n">
-        <v>144</v>
-      </c>
-      <c r="R414" t="n">
-        <v>2.723415071719434</v>
-      </c>
-      <c r="S414" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>140</v>
       </c>
       <c r="U414" t="inlineStr">
         <is>
-          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W414" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X414" t="inlineStr">
+        <is>
+          <t>Kikhoste</t>
+        </is>
+      </c>
+      <c r="Y414" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z414" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA414" t="inlineStr">
@@ -75527,6 +75450,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB414" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC414" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD414" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE414" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF414" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG414" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH414" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI414" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ414" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK414" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM414" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN414" t="b">
+        <v>1</v>
+      </c>
       <c r="AO414" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -75534,7 +75515,7 @@
       </c>
       <c r="AP414" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ414" t="inlineStr">
@@ -75542,57 +75523,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR414" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS414" t="inlineStr">
         <is>
-          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
+          <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
       <c r="AT414" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU414" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV414" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW414" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX414" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY414" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ414" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA414" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB414" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC414" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -75619,7 +75605,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -75668,98 +75654,23 @@
       <c r="O415" t="n">
         <v>144</v>
       </c>
+      <c r="R415" t="n">
+        <v>2.723415071719434</v>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U415" t="inlineStr">
         <is>
           <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
-      <c r="V415" t="inlineStr">
-        <is>
-          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W415" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X415" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y415" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z415" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA415" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB415" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC415" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD415" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE415" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF415" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG415" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH415" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI415" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ415" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK415" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly pertussis notifications.</t>
-        </is>
-      </c>
-      <c r="AM415" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN415" t="b">
-        <v>1</v>
       </c>
       <c r="AO415" t="inlineStr">
         <is>
@@ -75853,17 +75764,17 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -75897,22 +75808,39 @@
         </is>
       </c>
       <c r="N416" t="n">
-        <v>22</v>
+        <v>144</v>
       </c>
       <c r="O416" t="n">
-        <v>22</v>
-      </c>
-      <c r="R416" t="n">
-        <v>0.2055873694222336</v>
-      </c>
-      <c r="S416" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>144</v>
       </c>
       <c r="U416" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W416" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X416" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y416" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z416" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA416" t="inlineStr">
@@ -75920,6 +75848,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB416" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC416" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD416" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE416" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF416" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG416" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH416" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI416" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ416" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK416" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly pertussis notifications.</t>
+        </is>
+      </c>
+      <c r="AM416" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN416" t="b">
+        <v>1</v>
+      </c>
       <c r="AO416" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -75927,7 +75913,7 @@
       </c>
       <c r="AP416" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ416" t="inlineStr">
@@ -75935,62 +75921,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR416" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS416" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+          <t>SER_NZ_PERTUSSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT416" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU416" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV416" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW416" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX416" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY416" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ416" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA416" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB416" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC416" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -76017,7 +75998,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -76066,98 +76047,23 @@
       <c r="O417" t="n">
         <v>22</v>
       </c>
+      <c r="R417" t="n">
+        <v>0.2055873694222336</v>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U417" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
         </is>
       </c>
-      <c r="V417" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W417" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X417" t="inlineStr">
-        <is>
-          <t>Kikhosta</t>
-        </is>
-      </c>
-      <c r="Y417" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z417" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA417" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB417" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC417" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD417" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE417" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF417" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG417" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH417" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI417" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ417" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK417" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM417" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN417" t="b">
-        <v>1</v>
       </c>
       <c r="AO417" t="inlineStr">
         <is>
@@ -76256,17 +76162,17 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -76300,81 +76206,175 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="O418" t="n">
-        <v>74</v>
-      </c>
-      <c r="R418" t="n">
-        <v>0.02120128218249345</v>
-      </c>
-      <c r="S418" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V418" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W418" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X418" t="inlineStr">
+        <is>
+          <t>Kikhosta</t>
+        </is>
+      </c>
+      <c r="Y418" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z418" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA418" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB418" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC418" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD418" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE418" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF418" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG418" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH418" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI418" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ418" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK418" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM418" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN418" t="b">
+        <v>1</v>
       </c>
       <c r="AO418" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP418" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ418" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR418" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS418" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS418" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT418" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU418" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV418" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW418" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX418" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY418" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ418" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA418" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB418" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC418" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -76406,12 +76406,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -76436,7 +76436,7 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
@@ -76445,13 +76445,13 @@
         </is>
       </c>
       <c r="N419" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="O419" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="R419" t="n">
-        <v>0.05717658852960364</v>
+        <v>0.02120128218249345</v>
       </c>
       <c r="S419" t="inlineStr">
         <is>
@@ -76484,42 +76484,42 @@
       </c>
       <c r="AV419" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW419" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX419" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY419" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ419" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA419" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB419" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC419" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -76551,12 +76551,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -76590,93 +76590,81 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="O420" t="n">
-        <v>2</v>
-      </c>
-      <c r="P420" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="R420" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.05717658852960364</v>
       </c>
       <c r="S420" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA420" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO420" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP420" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ420" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS420" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR420" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS420" t="inlineStr"/>
       <c r="AT420" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU420" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV420" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW420" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX420" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY420" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ420" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA420" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB420" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC420" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -76703,7 +76691,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -76755,98 +76743,18 @@
       <c r="P421" t="n">
         <v>2</v>
       </c>
-      <c r="U421" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V421" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W421" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X421" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y421" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z421" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R421" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA421" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB421" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC421" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD421" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE421" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF421" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG421" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH421" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI421" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ421" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK421" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM421" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN421" t="b">
-        <v>1</v>
       </c>
       <c r="AO421" t="inlineStr">
         <is>
@@ -76940,17 +76848,17 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -76975,7 +76883,7 @@
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M422" t="inlineStr">
@@ -76984,81 +76892,173 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="O422" t="n">
-        <v>67</v>
-      </c>
-      <c r="R422" t="n">
-        <v>0.01919575548955488</v>
-      </c>
-      <c r="S422" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P422" t="n">
+        <v>2</v>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W422" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X422" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y422" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z422" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA422" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB422" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC422" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD422" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE422" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF422" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG422" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH422" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI422" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ422" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK422" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM422" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN422" t="b">
+        <v>1</v>
       </c>
       <c r="AO422" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP422" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR422" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS422" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ422" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS422" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT422" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU422" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV422" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW422" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX422" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY422" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ422" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA422" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB422" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC422" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -77090,12 +77090,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -77120,7 +77120,7 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
@@ -77129,13 +77129,13 @@
         </is>
       </c>
       <c r="N423" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="O423" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="R423" t="n">
-        <v>0.06207743897499823</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S423" t="inlineStr">
         <is>
@@ -77168,42 +77168,42 @@
       </c>
       <c r="AV423" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW423" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX423" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY423" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ423" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA423" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB423" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC423" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -77235,12 +77235,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -77274,93 +77274,81 @@
         </is>
       </c>
       <c r="N424" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="O424" t="n">
-        <v>2</v>
-      </c>
-      <c r="P424" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="R424" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.06207743897499823</v>
       </c>
       <c r="S424" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA424" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO424" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP424" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ424" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS424" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR424" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS424" t="inlineStr"/>
       <c r="AT424" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU424" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV424" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW424" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX424" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY424" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ424" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA424" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB424" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC424" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -77387,7 +77375,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -77439,98 +77427,18 @@
       <c r="P425" t="n">
         <v>2</v>
       </c>
-      <c r="U425" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V425" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W425" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X425" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y425" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z425" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R425" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA425" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB425" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC425" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD425" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE425" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF425" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG425" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH425" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI425" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ425" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK425" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM425" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN425" t="b">
-        <v>1</v>
       </c>
       <c r="AO425" t="inlineStr">
         <is>
@@ -77624,17 +77532,17 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -77659,7 +77567,7 @@
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
@@ -77668,81 +77576,173 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="O426" t="n">
-        <v>65</v>
-      </c>
-      <c r="R426" t="n">
-        <v>0.018622747863001</v>
-      </c>
-      <c r="S426" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P426" t="n">
+        <v>2</v>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V426" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W426" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X426" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y426" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z426" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA426" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB426" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC426" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD426" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE426" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF426" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG426" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH426" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI426" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ426" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK426" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM426" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN426" t="b">
+        <v>1</v>
       </c>
       <c r="AO426" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP426" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR426" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS426" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ426" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS426" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT426" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU426" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV426" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW426" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX426" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY426" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ426" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA426" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB426" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC426" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -77774,12 +77774,12 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -77804,7 +77804,7 @@
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
@@ -77813,13 +77813,13 @@
         </is>
       </c>
       <c r="N427" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="O427" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="R427" t="n">
-        <v>0.02287063541184146</v>
+        <v>0.018622747863001</v>
       </c>
       <c r="S427" t="inlineStr">
         <is>
@@ -77852,42 +77852,42 @@
       </c>
       <c r="AV427" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW427" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX427" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY427" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ427" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA427" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB427" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC427" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -77919,12 +77919,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -77958,93 +77958,81 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="O428" t="n">
-        <v>3</v>
-      </c>
-      <c r="P428" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="R428" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.02287063541184146</v>
       </c>
       <c r="S428" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA428" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO428" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP428" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ428" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS428" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR428" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS428" t="inlineStr"/>
       <c r="AT428" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU428" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV428" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW428" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX428" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY428" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ428" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA428" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB428" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC428" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -78071,7 +78059,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -78123,98 +78111,18 @@
       <c r="P429" t="n">
         <v>3</v>
       </c>
-      <c r="U429" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V429" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W429" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X429" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y429" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z429" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R429" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA429" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB429" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC429" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD429" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE429" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF429" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG429" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH429" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI429" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ429" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK429" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM429" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN429" t="b">
-        <v>1</v>
       </c>
       <c r="AO429" t="inlineStr">
         <is>
@@ -78308,17 +78216,17 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -78343,7 +78251,7 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
@@ -78352,81 +78260,173 @@
         </is>
       </c>
       <c r="N430" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="O430" t="n">
-        <v>80</v>
-      </c>
-      <c r="R430" t="n">
-        <v>0.02292030506215508</v>
-      </c>
-      <c r="S430" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P430" t="n">
+        <v>3</v>
+      </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V430" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W430" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X430" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y430" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z430" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA430" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB430" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC430" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD430" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE430" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF430" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG430" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH430" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI430" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ430" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK430" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM430" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN430" t="b">
+        <v>1</v>
       </c>
       <c r="AO430" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP430" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR430" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS430" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ430" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS430" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT430" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU430" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV430" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW430" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX430" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY430" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ430" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA430" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB430" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC430" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -78458,12 +78458,12 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -78488,7 +78488,7 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
@@ -78497,13 +78497,13 @@
         </is>
       </c>
       <c r="N431" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="O431" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="R431" t="n">
-        <v>0.05390935489934058</v>
+        <v>0.02292030506215508</v>
       </c>
       <c r="S431" t="inlineStr">
         <is>
@@ -78536,42 +78536,42 @@
       </c>
       <c r="AV431" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW431" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX431" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY431" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ431" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA431" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB431" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC431" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -78603,12 +78603,12 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -78642,93 +78642,81 @@
         </is>
       </c>
       <c r="N432" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="O432" t="n">
-        <v>2</v>
-      </c>
-      <c r="P432" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="R432" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.05390935489934058</v>
       </c>
       <c r="S432" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA432" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO432" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP432" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ432" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS432" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR432" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS432" t="inlineStr"/>
       <c r="AT432" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU432" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV432" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW432" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX432" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY432" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ432" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA432" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB432" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC432" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -78755,7 +78743,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -78807,98 +78795,18 @@
       <c r="P433" t="n">
         <v>2</v>
       </c>
-      <c r="U433" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V433" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W433" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X433" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y433" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z433" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R433" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S433" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA433" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB433" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC433" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD433" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE433" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF433" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG433" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH433" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI433" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ433" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK433" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM433" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN433" t="b">
-        <v>1</v>
       </c>
       <c r="AO433" t="inlineStr">
         <is>
@@ -78992,17 +78900,17 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -79027,7 +78935,7 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
@@ -79036,81 +78944,173 @@
         </is>
       </c>
       <c r="N434" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="O434" t="n">
-        <v>67</v>
-      </c>
-      <c r="R434" t="n">
-        <v>0.01919575548955488</v>
-      </c>
-      <c r="S434" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P434" t="n">
+        <v>2</v>
+      </c>
+      <c r="U434" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W434" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X434" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y434" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z434" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA434" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB434" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC434" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD434" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE434" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF434" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG434" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH434" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI434" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ434" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK434" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM434" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN434" t="b">
+        <v>1</v>
       </c>
       <c r="AO434" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP434" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR434" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS434" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ434" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS434" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT434" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU434" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV434" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW434" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX434" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY434" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ434" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA434" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB434" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC434" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -79142,12 +79142,12 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -79172,7 +79172,7 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
@@ -79181,13 +79181,13 @@
         </is>
       </c>
       <c r="N435" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="O435" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="R435" t="n">
-        <v>0.04329084560098561</v>
+        <v>0.01919575548955488</v>
       </c>
       <c r="S435" t="inlineStr">
         <is>
@@ -79220,42 +79220,42 @@
       </c>
       <c r="AV435" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW435" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX435" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY435" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ435" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA435" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB435" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC435" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -79287,12 +79287,12 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -79326,93 +79326,81 @@
         </is>
       </c>
       <c r="N436" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="O436" t="n">
-        <v>2</v>
-      </c>
-      <c r="P436" t="n">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="R436" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.04329084560098561</v>
       </c>
       <c r="S436" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA436" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO436" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP436" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ436" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS436" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR436" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS436" t="inlineStr"/>
       <c r="AT436" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU436" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV436" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW436" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX436" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY436" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ436" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA436" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB436" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC436" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -79439,7 +79427,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -79491,98 +79479,18 @@
       <c r="P437" t="n">
         <v>2</v>
       </c>
-      <c r="U437" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V437" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W437" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X437" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y437" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z437" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R437" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA437" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB437" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC437" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD437" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE437" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF437" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG437" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH437" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI437" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ437" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK437" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM437" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN437" t="b">
-        <v>1</v>
       </c>
       <c r="AO437" t="inlineStr">
         <is>
@@ -79676,17 +79584,17 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -79711,90 +79619,182 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N438" t="n">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="O438" t="n">
-        <v>78</v>
-      </c>
-      <c r="R438" t="n">
-        <v>0.2864793219225436</v>
-      </c>
-      <c r="S438" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P438" t="n">
+        <v>2</v>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W438" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X438" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y438" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z438" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA438" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB438" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC438" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD438" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE438" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF438" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG438" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH438" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI438" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ438" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK438" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM438" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN438" t="b">
+        <v>1</v>
       </c>
       <c r="AO438" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP438" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR438" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS438" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ438" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS438" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
       <c r="AT438" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU438" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV438" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW438" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX438" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY438" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ438" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA438" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB438" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC438" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -79826,12 +79826,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -79865,13 +79865,13 @@
         </is>
       </c>
       <c r="N439" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="O439" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="R439" t="n">
-        <v>0.0004682466352329422</v>
+        <v>0.2864793219225436</v>
       </c>
       <c r="S439" t="inlineStr">
         <is>
@@ -79904,42 +79904,42 @@
       </c>
       <c r="AV439" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW439" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX439" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY439" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ439" t="inlineStr">
         <is>
-          <t>sinan_datasus</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA439" t="inlineStr">
         <is>
-          <t>Brazil DATASUS SINAN</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB439" t="inlineStr">
         <is>
-          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC439" t="inlineStr">
         <is>
-          <t>ftp_dbc</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -79971,12 +79971,12 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -80010,100 +80010,81 @@
         </is>
       </c>
       <c r="N440" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O440" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R440" t="n">
-        <v>0.569218934676524</v>
+        <v>0.01451564569222121</v>
       </c>
       <c r="S440" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="AA440" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO440" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP440" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ440" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR440" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS440" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS440" t="inlineStr"/>
       <c r="AT440" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU440" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV440" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW440" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX440" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY440" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ440" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA440" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB440" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC440" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -80130,7 +80111,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -80174,103 +80155,28 @@
         </is>
       </c>
       <c r="N441" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="O441" t="n">
-        <v>32</v>
+        <v>47</v>
+      </c>
+      <c r="R441" t="n">
+        <v>0.8360403103061447</v>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U441" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_500</t>
         </is>
       </c>
-      <c r="V441" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_500</t>
-        </is>
-      </c>
-      <c r="W441" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X441" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y441" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z441" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA441" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB441" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC441" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD441" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE441" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF441" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG441" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH441" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI441" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ441" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK441" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
-        </is>
-      </c>
-      <c r="AM441" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN441" t="b">
-        <v>1</v>
       </c>
       <c r="AO441" t="inlineStr">
         <is>
@@ -80369,17 +80275,17 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -80413,81 +80319,175 @@
         </is>
       </c>
       <c r="N442" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="O442" t="n">
-        <v>14</v>
-      </c>
-      <c r="R442" t="n">
-        <v>0.02713157893308864</v>
-      </c>
-      <c r="S442" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>47</v>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="W442" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X442" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y442" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z442" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB442" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC442" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD442" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE442" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF442" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG442" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH442" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI442" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ442" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK442" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
+        </is>
+      </c>
+      <c r="AM442" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN442" t="b">
+        <v>1</v>
       </c>
       <c r="AO442" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP442" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ442" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR442" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS442" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS442" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
       <c r="AT442" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU442" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV442" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW442" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX442" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY442" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ442" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA442" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB442" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC442" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -80519,12 +80519,12 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -80558,100 +80558,81 @@
         </is>
       </c>
       <c r="N443" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="O443" t="n">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="R443" t="n">
-        <v>1.079075253735259</v>
+        <v>0.03488345862825683</v>
       </c>
       <c r="S443" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA443" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO443" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP443" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ443" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR443" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS443" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS443" t="inlineStr"/>
       <c r="AT443" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU443" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV443" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW443" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX443" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY443" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ443" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA443" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB443" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC443" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -80678,7 +80659,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -80722,103 +80703,28 @@
         </is>
       </c>
       <c r="N444" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="O444" t="n">
-        <v>61</v>
+        <v>97</v>
+      </c>
+      <c r="R444" t="n">
+        <v>1.715906551021641</v>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U444" t="inlineStr">
         <is>
           <t>SER_NO_FHI_101_MONTHLY</t>
         </is>
       </c>
-      <c r="V444" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_101_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W444" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X444" t="inlineStr">
-        <is>
-          <t>Kikhoste</t>
-        </is>
-      </c>
-      <c r="Y444" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z444" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA444" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB444" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC444" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD444" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE444" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF444" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG444" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH444" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI444" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ444" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK444" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM444" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN444" t="b">
-        <v>1</v>
       </c>
       <c r="AO444" t="inlineStr">
         <is>
@@ -80917,17 +80823,17 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -80952,7 +80858,7 @@
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M445" t="inlineStr">
@@ -80961,81 +80867,175 @@
         </is>
       </c>
       <c r="N445" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="O445" t="n">
-        <v>72</v>
-      </c>
-      <c r="R445" t="n">
-        <v>0.02062827455593957</v>
-      </c>
-      <c r="S445" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>97</v>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W445" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X445" t="inlineStr">
+        <is>
+          <t>Kikhoste</t>
+        </is>
+      </c>
+      <c r="Y445" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z445" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB445" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC445" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD445" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE445" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF445" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG445" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH445" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI445" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ445" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK445" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM445" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN445" t="b">
+        <v>1</v>
       </c>
       <c r="AO445" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP445" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ445" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR445" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS445" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS445" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_101_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT445" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU445" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV445" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW445" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ445" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA445" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB445" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC445" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -81067,12 +81067,12 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -81097,7 +81097,7 @@
       </c>
       <c r="L446" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M446" t="inlineStr">
@@ -81106,13 +81106,13 @@
         </is>
       </c>
       <c r="N446" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="O446" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="R446" t="n">
-        <v>0.03757318674802525</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S446" t="inlineStr">
         <is>
@@ -81145,42 +81145,42 @@
       </c>
       <c r="AV446" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW446" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX446" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY446" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ446" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA446" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB446" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC446" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -81212,12 +81212,12 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -81251,93 +81251,81 @@
         </is>
       </c>
       <c r="N447" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="O447" t="n">
-        <v>2</v>
-      </c>
-      <c r="P447" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="R447" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.03757318674802525</v>
       </c>
       <c r="S447" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA447" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO447" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP447" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ447" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS447" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR447" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS447" t="inlineStr"/>
       <c r="AT447" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU447" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV447" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW447" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX447" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY447" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ447" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA447" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB447" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC447" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -81364,7 +81352,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -81416,98 +81404,18 @@
       <c r="P448" t="n">
         <v>2</v>
       </c>
-      <c r="U448" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="V448" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PERTUSSIS</t>
-        </is>
-      </c>
-      <c r="W448" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X448" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="Y448" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z448" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R448" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA448" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB448" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC448" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD448" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE448" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF448" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG448" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH448" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI448" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ448" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK448" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM448" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN448" t="b">
-        <v>1</v>
       </c>
       <c r="AO448" t="inlineStr">
         <is>
@@ -81601,123 +81509,1044 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N449" t="n">
+        <v>2</v>
+      </c>
+      <c r="O449" t="n">
+        <v>2</v>
+      </c>
+      <c r="P449" t="n">
+        <v>2</v>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V449" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W449" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X449" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y449" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z449" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA449" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB449" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC449" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD449" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE449" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF449" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG449" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH449" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI449" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ449" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK449" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM449" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN449" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO449" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP449" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ449" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS449" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="AT449" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU449" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV449" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW449" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX449" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY449" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA449" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB449" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC449" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F449" t="inlineStr">
+      <c r="F450" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G449" t="inlineStr">
+      <c r="G450" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H449" t="inlineStr">
-        <is>
-          <t>D028</t>
-        </is>
-      </c>
-      <c r="I449" t="inlineStr">
-        <is>
-          <t>Pertussis</t>
-        </is>
-      </c>
-      <c r="J449" t="inlineStr">
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
         <is>
           <t>百日咳</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr">
+      <c r="K450" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L449" t="inlineStr">
+      <c r="L450" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="M449" t="inlineStr">
+      <c r="M450" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N449" t="n">
+      <c r="N450" t="n">
         <v>74</v>
       </c>
-      <c r="O449" t="n">
+      <c r="O450" t="n">
         <v>74</v>
       </c>
-      <c r="R449" t="n">
+      <c r="R450" t="n">
         <v>0.02120128218249345</v>
       </c>
-      <c r="S449" t="inlineStr">
+      <c r="S450" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO449" t="inlineStr">
+      <c r="AO450" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP449" t="inlineStr">
+      <c r="AP450" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR449" t="inlineStr">
+      <c r="AR450" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS449" t="inlineStr"/>
-      <c r="AT449" t="n">
+      <c r="AS450" t="inlineStr"/>
+      <c r="AT450" t="n">
         <v>0</v>
       </c>
-      <c r="AU449" t="inlineStr">
+      <c r="AU450" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV449" t="inlineStr">
+      <c r="AV450" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW449" t="inlineStr">
+      <c r="AW450" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX449" t="inlineStr">
+      <c r="AX450" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY449" t="inlineStr">
+      <c r="AY450" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ449" t="inlineStr">
+      <c r="AZ450" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA449" t="inlineStr">
+      <c r="BA450" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB449" t="inlineStr">
+      <c r="BB450" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC449" t="inlineStr">
+      <c r="BC450" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N451" t="n">
+        <v>57</v>
+      </c>
+      <c r="O451" t="n">
+        <v>57</v>
+      </c>
+      <c r="R451" t="n">
+        <v>0.04655807923124868</v>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO451" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP451" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR451" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS451" t="inlineStr"/>
+      <c r="AT451" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU451" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV451" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW451" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX451" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY451" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ451" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA451" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB451" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC451" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N452" t="n">
+        <v>2</v>
+      </c>
+      <c r="O452" t="n">
+        <v>2</v>
+      </c>
+      <c r="P452" t="n">
+        <v>2</v>
+      </c>
+      <c r="R452" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA452" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO452" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP452" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ452" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS452" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="AT452" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU452" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV452" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW452" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX452" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY452" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ452" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA452" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB452" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC452" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N453" t="n">
+        <v>2</v>
+      </c>
+      <c r="O453" t="n">
+        <v>2</v>
+      </c>
+      <c r="P453" t="n">
+        <v>2</v>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V453" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W453" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X453" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y453" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z453" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA453" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB453" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC453" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD453" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE453" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF453" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG453" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH453" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI453" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ453" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK453" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM453" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN453" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO453" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP453" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ453" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS453" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="AT453" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU453" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV453" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW453" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX453" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY453" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ453" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA453" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB453" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC453" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N454" t="n">
+        <v>76</v>
+      </c>
+      <c r="O454" t="n">
+        <v>76</v>
+      </c>
+      <c r="R454" t="n">
+        <v>0.02177428980904733</v>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO454" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP454" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR454" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS454" t="inlineStr"/>
+      <c r="AT454" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU454" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV454" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW454" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX454" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY454" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ454" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA454" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB454" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC454" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -81756,7 +82585,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -81839,7 +82668,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -81849,7 +82678,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11">
@@ -81869,7 +82698,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -81901,7 +82730,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30418</v>
+        <v>30766</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -73506,13 +73506,13 @@
         </is>
       </c>
       <c r="N401" t="n">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="O401" t="n">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="R401" t="n">
-        <v>4.084166743306007</v>
+        <v>4.098857990584086</v>
       </c>
       <c r="S401" t="inlineStr">
         <is>
@@ -82945,13 +82945,13 @@
         </is>
       </c>
       <c r="N455" t="n">
-        <v>78</v>
+        <v>1048</v>
       </c>
       <c r="O455" t="n">
-        <v>78</v>
+        <v>1048</v>
       </c>
       <c r="R455" t="n">
-        <v>0.2864793219225436</v>
+        <v>3.84910678685674</v>
       </c>
       <c r="S455" t="inlineStr">
         <is>
@@ -83235,13 +83235,13 @@
         </is>
       </c>
       <c r="N457" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="O457" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="R457" t="n">
-        <v>0.8360403103061447</v>
+        <v>1.0317093191012</v>
       </c>
       <c r="S457" t="inlineStr">
         <is>
@@ -83399,10 +83399,10 @@
         </is>
       </c>
       <c r="N458" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="O458" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="U458" t="inlineStr">
         <is>
@@ -83638,13 +83638,13 @@
         </is>
       </c>
       <c r="N459" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O459" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="R459" t="n">
-        <v>0.03488345862825683</v>
+        <v>0.04263533832342501</v>
       </c>
       <c r="S459" t="inlineStr">
         <is>
@@ -85629,6 +85629,1238 @@
       <c r="BC470" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N471" t="n">
+        <v>91</v>
+      </c>
+      <c r="O471" t="n">
+        <v>91</v>
+      </c>
+      <c r="R471" t="n">
+        <v>0.07432956508848473</v>
+      </c>
+      <c r="S471" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO471" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP471" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR471" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS471" t="inlineStr"/>
+      <c r="AT471" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU471" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV471" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW471" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX471" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY471" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ471" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA471" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB471" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC471" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N472" t="n">
+        <v>2</v>
+      </c>
+      <c r="O472" t="n">
+        <v>2</v>
+      </c>
+      <c r="P472" t="n">
+        <v>2</v>
+      </c>
+      <c r="R472" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S472" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA472" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO472" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP472" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ472" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS472" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="AT472" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU472" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV472" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW472" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX472" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY472" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ472" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA472" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB472" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC472" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N473" t="n">
+        <v>2</v>
+      </c>
+      <c r="O473" t="n">
+        <v>2</v>
+      </c>
+      <c r="P473" t="n">
+        <v>2</v>
+      </c>
+      <c r="U473" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="V473" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="W473" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X473" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y473" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z473" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA473" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB473" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC473" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD473" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE473" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF473" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG473" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH473" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI473" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ473" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK473" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM473" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN473" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO473" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP473" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ473" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS473" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PERTUSSIS; SER_SG_HIST_PERTUSSIS</t>
+        </is>
+      </c>
+      <c r="AT473" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU473" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV473" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW473" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX473" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY473" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ473" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA473" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB473" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC473" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N474" t="n">
+        <v>33</v>
+      </c>
+      <c r="O474" t="n">
+        <v>33</v>
+      </c>
+      <c r="R474" t="n">
+        <v>0.009454625838138971</v>
+      </c>
+      <c r="S474" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO474" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP474" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR474" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS474" t="inlineStr"/>
+      <c r="AT474" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU474" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV474" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW474" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX474" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY474" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ474" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA474" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB474" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC474" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N475" t="n">
+        <v>0</v>
+      </c>
+      <c r="O475" t="n">
+        <v>0</v>
+      </c>
+      <c r="R475" t="n">
+        <v>0</v>
+      </c>
+      <c r="S475" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U475" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="AA475" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO475" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP475" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ475" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR475" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS475" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="AT475" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU475" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV475" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW475" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX475" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY475" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ475" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA475" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB475" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC475" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N476" t="n">
+        <v>0</v>
+      </c>
+      <c r="O476" t="n">
+        <v>0</v>
+      </c>
+      <c r="U476" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="V476" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="W476" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X476" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="Y476" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z476" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA476" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB476" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC476" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD476" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE476" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF476" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG476" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH476" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI476" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ476" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK476" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 500.</t>
+        </is>
+      </c>
+      <c r="AM476" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN476" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO476" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP476" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ476" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR476" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS476" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_500</t>
+        </is>
+      </c>
+      <c r="AT476" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU476" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV476" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW476" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX476" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY476" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ476" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA476" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB476" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC476" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>pertussis</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>D028</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Pertussis</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>百日咳</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N477" t="n">
+        <v>1</v>
+      </c>
+      <c r="O477" t="n">
+        <v>1</v>
+      </c>
+      <c r="R477" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO477" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP477" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR477" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS477" t="inlineStr"/>
+      <c r="AT477" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU477" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV477" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW477" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX477" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY477" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ477" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA477" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB477" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC477" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -85665,7 +86897,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -85748,7 +86980,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>306</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -85758,7 +86990,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11">
@@ -85778,7 +87010,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -85810,7 +87042,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30964</v>
+        <v>32080</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -73506,13 +73506,13 @@
         </is>
       </c>
       <c r="N401" t="n">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="O401" t="n">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="R401" t="n">
-        <v>4.098857990584086</v>
+        <v>4.102530802403606</v>
       </c>
       <c r="S401" t="inlineStr">
         <is>
@@ -82945,13 +82945,13 @@
         </is>
       </c>
       <c r="N455" t="n">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="O455" t="n">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="R455" t="n">
-        <v>3.84910678685674</v>
+        <v>3.874816469593379</v>
       </c>
       <c r="S455" t="inlineStr">
         <is>
@@ -87042,7 +87042,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32080</v>
+        <v>32088</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d028/2026-2029.xlsx
+++ b/diseases/d028/2026-2029.xlsx
@@ -6008,7 +6008,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -27099,7 +27099,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -38249,7 +38249,7 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN204" t="b">
@@ -48975,7 +48975,7 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN262" t="b">
@@ -59625,7 +59625,7 @@
       </c>
       <c r="AM322" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN322" t="b">
@@ -69682,7 +69682,7 @@
       </c>
       <c r="AM379" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN379" t="b">
@@ -78326,13 +78326,13 @@
         </is>
       </c>
       <c r="N429" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O429" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="R429" t="n">
-        <v>2.476566156113709</v>
+        <v>2.458876397855754</v>
       </c>
       <c r="S429" t="inlineStr">
         <is>
@@ -78490,10 +78490,10 @@
         </is>
       </c>
       <c r="N430" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O430" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="U430" t="inlineStr">
         <is>
@@ -78582,7 +78582,7 @@
       </c>
       <c r="AM430" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN430" t="b">
@@ -83235,13 +83235,13 @@
         </is>
       </c>
       <c r="N457" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O457" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R457" t="n">
-        <v>1.0317093191012</v>
+        <v>1.049497410809841</v>
       </c>
       <c r="S457" t="inlineStr">
         <is>
@@ -83399,10 +83399,10 @@
         </is>
       </c>
       <c r="N458" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O458" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U458" t="inlineStr">
         <is>
@@ -83783,13 +83783,13 @@
         </is>
       </c>
       <c r="N460" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="O460" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="R460" t="n">
-        <v>1.715906551021641</v>
+        <v>2.264289057018248</v>
       </c>
       <c r="S460" t="inlineStr">
         <is>
@@ -83947,10 +83947,10 @@
         </is>
       </c>
       <c r="N461" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="O461" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="U461" t="inlineStr">
         <is>
@@ -84039,7 +84039,7 @@
       </c>
       <c r="AM461" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN461" t="b">
@@ -86383,13 +86383,13 @@
         </is>
       </c>
       <c r="N475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R475" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S475" t="inlineStr">
         <is>
@@ -86547,10 +86547,10 @@
         </is>
       </c>
       <c r="N476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U476" t="inlineStr">
         <is>
@@ -87042,7 +87042,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32088</v>
+        <v>32120</v>
       </c>
     </row>
     <row r="16">
